--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,799 +558,1301 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>hQiNHHd2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.71363636363636</v>
+      </c>
+      <c r="D2" t="n">
+        <v>181.2214876033058</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>65.22892561983471</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1194283.05785124</v>
+      </c>
+      <c r="H2" t="n">
+        <v>69.74586776859505</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26.89177350427351</v>
+      </c>
+      <c r="J2" t="n">
+        <v>178.9333333333333</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.237393162393162</v>
+      </c>
+      <c r="L2" t="n">
+        <v>69.07382478632479</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2111908.653846154</v>
+      </c>
+      <c r="N2" t="n">
+        <v>72.68002136752136</v>
+      </c>
+      <c r="O2" t="n">
+        <v>24.8960601861682</v>
+      </c>
+      <c r="P2" t="n">
+        <v>179.2467124061383</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.005681818181818</v>
+      </c>
+      <c r="R2" t="n">
+        <v>64.4254476802456</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1339728.941621188</v>
+      </c>
+      <c r="T2" t="n">
+        <v>70.03738061847666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>24.22683843466923</v>
+      </c>
+      <c r="V2" t="n">
+        <v>178.1881626860897</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.09467744597052</v>
+      </c>
+      <c r="X2" t="n">
+        <v>64.07150436637666</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1654372.928225007</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>70.12545419528274</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>C6QBlj7R</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23.99173553719008</v>
+      </c>
+      <c r="D3" t="n">
+        <v>179.0082644628099</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="F3" t="n">
+        <v>66.1487603305785</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1373140.495867769</v>
+      </c>
+      <c r="H3" t="n">
+        <v>71.4504132231405</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26.25075757575758</v>
+      </c>
+      <c r="J3" t="n">
+        <v>181.259494949495</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.077373737373737</v>
+      </c>
+      <c r="L3" t="n">
+        <v>68.45560606060606</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2652094.696969697</v>
+      </c>
+      <c r="N3" t="n">
+        <v>71.88641414141414</v>
+      </c>
+      <c r="O3" t="n">
+        <v>23.50337957497048</v>
+      </c>
+      <c r="P3" t="n">
+        <v>180.1113975538019</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.111302533192485</v>
+      </c>
+      <c r="R3" t="n">
+        <v>65.34020277967646</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1410659.823629321</v>
+      </c>
+      <c r="T3" t="n">
+        <v>71.57224466123988</v>
+      </c>
+      <c r="U3" t="n">
+        <v>25.93281387108913</v>
+      </c>
+      <c r="V3" t="n">
+        <v>180.4210776096949</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.087470993414088</v>
+      </c>
+      <c r="X3" t="n">
+        <v>66.00285056358106</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1275156.067708577</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>70.95271845304453</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>dbI3Q902</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>25.94338842975207</v>
+      </c>
+      <c r="D4" t="n">
+        <v>182.3151515151515</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.016942148760331</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66.53985307621672</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1710660.69788797</v>
+      </c>
+      <c r="H4" t="n">
+        <v>71.34012855831038</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22.9301652892562</v>
+      </c>
+      <c r="J4" t="n">
+        <v>179.5735537190083</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="L4" t="n">
+        <v>67.41570247933883</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2702801.652892562</v>
+      </c>
+      <c r="N4" t="n">
+        <v>73.98719008264464</v>
+      </c>
+      <c r="O4" t="n">
+        <v>26.3548115008096</v>
+      </c>
+      <c r="P4" t="n">
+        <v>181.5160664571145</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.069618839271246</v>
+      </c>
+      <c r="R4" t="n">
+        <v>65.72389331534244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1763919.426395406</v>
+      </c>
+      <c r="T4" t="n">
+        <v>70.12543985297469</v>
+      </c>
+      <c r="U4" t="n">
+        <v>22.97745526449095</v>
+      </c>
+      <c r="V4" t="n">
+        <v>180.6305075680156</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.061565903160881</v>
+      </c>
+      <c r="X4" t="n">
+        <v>63.85222647700009</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1760370.73914639</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>72.04681839871215</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>26.43719008264463</v>
+      </c>
+      <c r="D5" t="n">
+        <v>184.098347107438</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.085950413223141</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.35619834710744</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1304522.727272727</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70.40826446280992</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.91418181818181</v>
+      </c>
+      <c r="J5" t="n">
+        <v>182.373494949495</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.053454545454546</v>
+      </c>
+      <c r="L5" t="n">
+        <v>66.88246464646465</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2310633.939393939</v>
+      </c>
+      <c r="N5" t="n">
+        <v>70.66101010101009</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22.61419658518765</v>
+      </c>
+      <c r="P5" t="n">
+        <v>182.8230366824126</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.007190324295588</v>
+      </c>
+      <c r="R5" t="n">
+        <v>60.82175798331512</v>
+      </c>
+      <c r="S5" t="n">
+        <v>833914.9144306846</v>
+      </c>
+      <c r="T5" t="n">
+        <v>70.53410923090419</v>
+      </c>
+      <c r="U5" t="n">
+        <v>24.98413223253168</v>
+      </c>
+      <c r="V5" t="n">
+        <v>180.3917009763468</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.032536380476884</v>
+      </c>
+      <c r="X5" t="n">
+        <v>62.88678790209655</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1320416.087505956</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>68.56651379315709</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26.5977392977393</v>
+      </c>
+      <c r="D6" t="n">
+        <v>182.7970177970178</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.647186147186147</v>
+      </c>
+      <c r="F6" t="n">
+        <v>72.65175565175566</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5751824.194324194</v>
+      </c>
+      <c r="H6" t="n">
+        <v>77.02780182780182</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.25123966942149</v>
+      </c>
+      <c r="J6" t="n">
+        <v>179.5227272727273</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>68.71115702479338</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3590258.26446281</v>
+      </c>
+      <c r="N6" t="n">
+        <v>72.81198347107438</v>
+      </c>
+      <c r="O6" t="n">
+        <v>23.95564720305985</v>
+      </c>
+      <c r="P6" t="n">
+        <v>184.2143542212206</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.20673345095614</v>
+      </c>
+      <c r="R6" t="n">
+        <v>67.00702322662185</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2723039.174069415</v>
+      </c>
+      <c r="T6" t="n">
+        <v>73.79395538385477</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24.61720744986158</v>
+      </c>
+      <c r="V6" t="n">
+        <v>181.210664237611</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>62.53636940526158</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1660687.617344629</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>67.53240486854197</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>8GUEN7pL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23.18452380952381</v>
+      </c>
+      <c r="D7" t="n">
+        <v>182.7202380952381</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>66.14550264550265</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1567420.634920635</v>
+      </c>
+      <c r="H7" t="n">
+        <v>71.96891534391534</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25.82644628099173</v>
+      </c>
+      <c r="J7" t="n">
+        <v>182.1239669421487</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.099173553719009</v>
+      </c>
+      <c r="L7" t="n">
+        <v>68.02892561983471</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2388946.280991735</v>
+      </c>
+      <c r="N7" t="n">
+        <v>71.65702479338843</v>
+      </c>
+      <c r="O7" t="n">
+        <v>21.49345883752257</v>
+      </c>
+      <c r="P7" t="n">
+        <v>181.312042785549</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>62.41485954484194</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1338945.401704054</v>
+      </c>
+      <c r="T7" t="n">
+        <v>71.52307167610287</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.76048416331712</v>
+      </c>
+      <c r="V7" t="n">
+        <v>181.2109385196535</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.099610786049221</v>
+      </c>
+      <c r="X7" t="n">
+        <v>65.44062488498329</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1417592.893425927</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>69.51482559206207</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>juKJMRaR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25.73254281949934</v>
+      </c>
+      <c r="D8" t="n">
+        <v>183.6514273166447</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.068379446640316</v>
+      </c>
+      <c r="F8" t="n">
+        <v>69.80013175230567</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3078094.861660079</v>
+      </c>
+      <c r="H8" t="n">
+        <v>73.36873078612209</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25.565</v>
+      </c>
+      <c r="J8" t="n">
+        <v>180.4613636363636</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>68.29863636363635</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3353909.090909091</v>
+      </c>
+      <c r="N8" t="n">
+        <v>72.40909090909091</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24.71766330980658</v>
+      </c>
+      <c r="P8" t="n">
+        <v>181.8119711303336</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.094622016722731</v>
+      </c>
+      <c r="R8" t="n">
+        <v>64.45120159149725</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1407061.527224356</v>
+      </c>
+      <c r="T8" t="n">
+        <v>70.01688413520806</v>
+      </c>
+      <c r="U8" t="n">
+        <v>23.93924948169194</v>
+      </c>
+      <c r="V8" t="n">
+        <v>181.0626345422125</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>64.16289839121521</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1582318.647846541</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>70.55857937973506</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>28.12</v>
+        <v>25.78471074380165</v>
       </c>
       <c r="D9" t="n">
-        <v>180.68</v>
+        <v>177.1685950413223</v>
       </c>
       <c r="E9" t="n">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>67.08</v>
+        <v>69.0400826446281</v>
       </c>
       <c r="G9" t="n">
-        <v>2060500</v>
+        <v>2688088.842975207</v>
       </c>
       <c r="H9" t="n">
-        <v>68.23999999999999</v>
+        <v>71.82314049586776</v>
       </c>
       <c r="I9" t="n">
-        <v>25.50181818181819</v>
+        <v>27.95029461279461</v>
       </c>
       <c r="J9" t="n">
-        <v>181.7490909090909</v>
+        <v>180.9389730639731</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>1.355765993265993</v>
       </c>
       <c r="L9" t="n">
-        <v>66.72727272727273</v>
+        <v>72.25223063973063</v>
       </c>
       <c r="M9" t="n">
-        <v>1934454.545454545</v>
+        <v>4156005.892255893</v>
       </c>
       <c r="N9" t="n">
-        <v>71.75090909090909</v>
+        <v>74.88489057239057</v>
       </c>
       <c r="O9" t="n">
-        <v>28.21197686584515</v>
+        <v>25.00575503391969</v>
       </c>
       <c r="P9" t="n">
-        <v>180.7195216228784</v>
+        <v>177.7087804701597</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.106161357823762</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>64.20897756335737</v>
+        <v>65.12309365160417</v>
       </c>
       <c r="S9" t="n">
-        <v>758086.4479190886</v>
+        <v>1178422.422612406</v>
       </c>
       <c r="T9" t="n">
-        <v>66.2144094396652</v>
+        <v>69.32110179854355</v>
       </c>
       <c r="U9" t="n">
-        <v>25.5717400246812</v>
+        <v>25.30319930495762</v>
       </c>
       <c r="V9" t="n">
-        <v>182.6749691484985</v>
+        <v>179.407554828247</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0375</v>
+        <v>1.009185932827237</v>
       </c>
       <c r="X9" t="n">
-        <v>65.52012032085561</v>
+        <v>66.64130965992778</v>
       </c>
       <c r="Y9" t="n">
-        <v>1893707.836281366</v>
+        <v>1675512.968426472</v>
       </c>
       <c r="Z9" t="n">
-        <v>70.47415158371041</v>
+        <v>72.55957307543385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.17727272727273</v>
+        <v>26.74664031620554</v>
       </c>
       <c r="D10" t="n">
-        <v>180.8424242424242</v>
+        <v>180.6707509881423</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>1.120158102766798</v>
       </c>
       <c r="F10" t="n">
-        <v>64.67272727272727</v>
+        <v>67.65177865612648</v>
       </c>
       <c r="G10" t="n">
-        <v>1116234.848484849</v>
+        <v>1714124.505928854</v>
       </c>
       <c r="H10" t="n">
-        <v>69.65909090909092</v>
+        <v>70.82806324110672</v>
       </c>
       <c r="I10" t="n">
-        <v>26.15</v>
+        <v>26.28458498023715</v>
       </c>
       <c r="J10" t="n">
-        <v>179.7833333333333</v>
+        <v>182.0379446640316</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>1.220948616600791</v>
       </c>
       <c r="L10" t="n">
-        <v>68.3</v>
+        <v>65.15296442687747</v>
       </c>
       <c r="M10" t="n">
-        <v>2399250</v>
+        <v>2279567.193675889</v>
       </c>
       <c r="N10" t="n">
-        <v>71.56666666666666</v>
+        <v>68.43596837944663</v>
       </c>
       <c r="O10" t="n">
-        <v>24.81484348125215</v>
+        <v>25.37082425973347</v>
       </c>
       <c r="P10" t="n">
-        <v>177.1640897587105</v>
+        <v>179.4093828057581</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>1.068056283635067</v>
       </c>
       <c r="R10" t="n">
-        <v>64.25838954002653</v>
+        <v>63.659136656108</v>
       </c>
       <c r="S10" t="n">
-        <v>1228559.665094108</v>
+        <v>1149822.763135871</v>
       </c>
       <c r="T10" t="n">
-        <v>70.12398643667994</v>
+        <v>68.20801251527664</v>
       </c>
       <c r="U10" t="n">
-        <v>26.6525</v>
+        <v>23.42457216033726</v>
       </c>
       <c r="V10" t="n">
-        <v>180.8938888888889</v>
+        <v>179.5890564434515</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.134082025824141</v>
       </c>
       <c r="X10" t="n">
-        <v>66.58333333333333</v>
+        <v>63.11056648969047</v>
       </c>
       <c r="Y10" t="n">
-        <v>1613522.222222222</v>
+        <v>1506254.24927028</v>
       </c>
       <c r="Z10" t="n">
-        <v>69.64333333333333</v>
+        <v>68.98374969832784</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>26.50649350649351</v>
+        <v>27.46694214876033</v>
       </c>
       <c r="D11" t="n">
-        <v>180.1597402597402</v>
+        <v>183.595041322314</v>
       </c>
       <c r="E11" t="n">
-        <v>1.054545454545455</v>
+        <v>1.140495867768595</v>
       </c>
       <c r="F11" t="n">
-        <v>64.80129870129871</v>
+        <v>68.4504132231405</v>
       </c>
       <c r="G11" t="n">
-        <v>1105805.194805195</v>
+        <v>3114628.099173554</v>
       </c>
       <c r="H11" t="n">
-        <v>68.69870129870129</v>
+        <v>70.30165289256199</v>
       </c>
       <c r="I11" t="n">
-        <v>24.82626262626262</v>
+        <v>28.16198347107438</v>
       </c>
       <c r="J11" t="n">
-        <v>181.6225589225589</v>
+        <v>179.95</v>
       </c>
       <c r="K11" t="n">
-        <v>1.171043771043771</v>
+        <v>1.133471074380165</v>
       </c>
       <c r="L11" t="n">
-        <v>66.11632996632996</v>
+        <v>67.30330578512397</v>
       </c>
       <c r="M11" t="n">
-        <v>1932807.239057239</v>
+        <v>2102035.123966943</v>
       </c>
       <c r="N11" t="n">
-        <v>70.58400673400673</v>
+        <v>68.47851239669421</v>
       </c>
       <c r="O11" t="n">
-        <v>26.23673094367766</v>
+        <v>27.71215289806927</v>
       </c>
       <c r="P11" t="n">
-        <v>180.5423467618793</v>
+        <v>182.8710439402841</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.062692445399213</v>
+        <v>1.033642822921479</v>
       </c>
       <c r="R11" t="n">
-        <v>64.12625996102622</v>
+        <v>65.16996355613736</v>
       </c>
       <c r="S11" t="n">
-        <v>1050841.846817779</v>
+        <v>1114421.514256494</v>
       </c>
       <c r="T11" t="n">
-        <v>67.60111380936814</v>
+        <v>66.44048466096001</v>
       </c>
       <c r="U11" t="n">
-        <v>23.14491129785247</v>
+        <v>28.29888045459057</v>
       </c>
       <c r="V11" t="n">
-        <v>182.597268907563</v>
+        <v>181.0575193027864</v>
       </c>
       <c r="W11" t="n">
-        <v>1.019607843137255</v>
+        <v>1.272133152389121</v>
       </c>
       <c r="X11" t="n">
-        <v>61.33384687208217</v>
+        <v>65.19175011272924</v>
       </c>
       <c r="Y11" t="n">
-        <v>937075.1633986927</v>
+        <v>1132258.644866073</v>
       </c>
       <c r="Z11" t="n">
-        <v>69.2814659197012</v>
+        <v>66.99970275088936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>69kBKJCq</t>
+          <t>S0BoIo8r</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24.54444444444444</v>
+        <v>27.23321678321679</v>
       </c>
       <c r="D12" t="n">
-        <v>180.0018518518518</v>
+        <v>179.9846153846154</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>1.055244755244755</v>
       </c>
       <c r="F12" t="n">
-        <v>65.91296296296296</v>
+        <v>66.32447552447553</v>
       </c>
       <c r="G12" t="n">
-        <v>1544296.296296296</v>
+        <v>1243762.237762238</v>
       </c>
       <c r="H12" t="n">
-        <v>70.24444444444445</v>
+        <v>69.24999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>25.08</v>
+        <v>26.81570247933884</v>
       </c>
       <c r="J12" t="n">
-        <v>179.14</v>
+        <v>179.7136363636364</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.19297520661157</v>
       </c>
       <c r="L12" t="n">
-        <v>67.09999999999999</v>
+        <v>69.66198347107438</v>
       </c>
       <c r="M12" t="n">
-        <v>2075100</v>
+        <v>2844318.181818182</v>
       </c>
       <c r="N12" t="n">
-        <v>72.75999999999999</v>
+        <v>72.40289256198348</v>
       </c>
       <c r="O12" t="n">
-        <v>21.42078843057104</v>
+        <v>25.32673159418616</v>
       </c>
       <c r="P12" t="n">
-        <v>180.968865353648</v>
+        <v>180.0282591981014</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>1.065582881395238</v>
       </c>
       <c r="R12" t="n">
-        <v>58.65328254676081</v>
+        <v>63.12229113593663</v>
       </c>
       <c r="S12" t="n">
-        <v>625703.7656385483</v>
+        <v>978096.9449809925</v>
       </c>
       <c r="T12" t="n">
-        <v>68.8248978075065</v>
+        <v>67.4862462413822</v>
       </c>
       <c r="U12" t="n">
-        <v>25.63211289092296</v>
+        <v>25.34541413226725</v>
       </c>
       <c r="V12" t="n">
-        <v>179.6620289855073</v>
+        <v>179.9661829976804</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.209683963984066</v>
       </c>
       <c r="X12" t="n">
-        <v>63.93570556826849</v>
+        <v>64.87542444927111</v>
       </c>
       <c r="Y12" t="n">
-        <v>1280134.553775744</v>
+        <v>2706357.989621043</v>
       </c>
       <c r="Z12" t="n">
-        <v>69.13422578184591</v>
+        <v>69.83993869212745</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.81990740740741</v>
+        <v>24.68801652892562</v>
       </c>
       <c r="D13" t="n">
-        <v>178.9263888888889</v>
+        <v>178.9306703397612</v>
       </c>
       <c r="E13" t="n">
-        <v>1.180555555555556</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>69.1962962962963</v>
+        <v>66.34825528007347</v>
       </c>
       <c r="G13" t="n">
-        <v>2201384.259259259</v>
+        <v>1942872.58953168</v>
       </c>
       <c r="H13" t="n">
-        <v>72.55787037037037</v>
+        <v>72.39931129476582</v>
       </c>
       <c r="I13" t="n">
-        <v>28.83030303030303</v>
+        <v>26.58287037037038</v>
       </c>
       <c r="J13" t="n">
-        <v>181.5651515151515</v>
+        <v>180.7279882154882</v>
       </c>
       <c r="K13" t="n">
-        <v>1.375757575757576</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>72.38939393939394</v>
+        <v>68.49570707070707</v>
       </c>
       <c r="M13" t="n">
-        <v>3985265.151515151</v>
+        <v>2260594.696969697</v>
       </c>
       <c r="N13" t="n">
-        <v>74.58939393939393</v>
+        <v>71.7898569023569</v>
       </c>
       <c r="O13" t="n">
-        <v>24.13045491143317</v>
+        <v>25.12751958758082</v>
       </c>
       <c r="P13" t="n">
-        <v>177.691807568438</v>
+        <v>178.7678221908926</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.133544685990338</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>65.72927737520128</v>
+        <v>64.15508470330329</v>
       </c>
       <c r="S13" t="n">
-        <v>2405915.006038647</v>
+        <v>1433586.134712753</v>
       </c>
       <c r="T13" t="n">
-        <v>72.39473631239935</v>
+        <v>70.36226541310856</v>
       </c>
       <c r="U13" t="n">
-        <v>24.02767352000089</v>
+        <v>25.97097007863313</v>
       </c>
       <c r="V13" t="n">
-        <v>178.6873755826441</v>
+        <v>180.740178362298</v>
       </c>
       <c r="W13" t="n">
-        <v>1.015579710144928</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>66.31051361255965</v>
+        <v>66.19686477220445</v>
       </c>
       <c r="Y13" t="n">
-        <v>1832160.41950377</v>
+        <v>1491495.73621829</v>
       </c>
       <c r="Z13" t="n">
-        <v>73.15825998383544</v>
+        <v>70.0151234851099</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MHXbihN8</t>
+          <t>Ik4bFqh1</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25.51969696969697</v>
+        <v>26.65398550724638</v>
       </c>
       <c r="D14" t="n">
-        <v>177.0681818181818</v>
+        <v>178.7695652173913</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>1.051811594202898</v>
       </c>
       <c r="F14" t="n">
-        <v>68.54545454545455</v>
+        <v>70.86437198067632</v>
       </c>
       <c r="G14" t="n">
-        <v>2561818.181818182</v>
+        <v>3801929.347826087</v>
       </c>
       <c r="H14" t="n">
-        <v>71.42878787878787</v>
+        <v>74.20760869565218</v>
       </c>
       <c r="I14" t="n">
-        <v>27.23636363636364</v>
+        <v>26.02596153846154</v>
       </c>
       <c r="J14" t="n">
-        <v>181.3818181818182</v>
+        <v>179.2244755244755</v>
       </c>
       <c r="K14" t="n">
-        <v>1.181818181818182</v>
+        <v>1.172027972027972</v>
       </c>
       <c r="L14" t="n">
-        <v>68.47272727272727</v>
+        <v>67.13505244755244</v>
       </c>
       <c r="M14" t="n">
-        <v>1979545.454545455</v>
+        <v>3631690.996503497</v>
       </c>
       <c r="N14" t="n">
-        <v>71.38181818181818</v>
+        <v>71.62867132867133</v>
       </c>
       <c r="O14" t="n">
-        <v>24.89524304833229</v>
+        <v>24.31039263523147</v>
       </c>
       <c r="P14" t="n">
-        <v>177.8864121766868</v>
+        <v>178.8956095957849</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>1.038273329034857</v>
       </c>
       <c r="R14" t="n">
-        <v>64.84929443173149</v>
+        <v>65.03243073543409</v>
       </c>
       <c r="S14" t="n">
-        <v>1214233.626308855</v>
+        <v>1656006.346237286</v>
       </c>
       <c r="T14" t="n">
-        <v>69.44527771999168</v>
+        <v>70.23552372359221</v>
       </c>
       <c r="U14" t="n">
-        <v>25.017854098161</v>
+        <v>25.39949988914902</v>
       </c>
       <c r="V14" t="n">
-        <v>178.7019333820485</v>
+        <v>179.0138150104058</v>
       </c>
       <c r="W14" t="n">
-        <v>1.035714285714286</v>
+        <v>1.01875528317836</v>
       </c>
       <c r="X14" t="n">
-        <v>63.11455364754597</v>
+        <v>65.3416282588304</v>
       </c>
       <c r="Y14" t="n">
-        <v>972242.373036171</v>
+        <v>1654473.976252508</v>
       </c>
       <c r="Z14" t="n">
-        <v>67.75368408232859</v>
+        <v>70.39790496008256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>p0lFJwSk</t>
+          <t>dt32E377</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>26.08333333333333</v>
+        <v>26.54545454545455</v>
       </c>
       <c r="D15" t="n">
-        <v>178.25</v>
+        <v>178.4917355371901</v>
       </c>
       <c r="E15" t="n">
-        <v>1.033333333333333</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>70.50740740740741</v>
+        <v>69.73140495867769</v>
       </c>
       <c r="G15" t="n">
-        <v>3627407.407407407</v>
+        <v>2881012.396694215</v>
       </c>
       <c r="H15" t="n">
-        <v>74.27407407407408</v>
+        <v>72.39256198347107</v>
       </c>
       <c r="I15" t="n">
-        <v>26.41818181818182</v>
+        <v>25.22988980716253</v>
       </c>
       <c r="J15" t="n">
-        <v>178.0727272727273</v>
+        <v>181.8916896235078</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>1.183011937557392</v>
       </c>
       <c r="L15" t="n">
-        <v>69.41818181818181</v>
+        <v>67.16726354453627</v>
       </c>
       <c r="M15" t="n">
-        <v>2855000</v>
+        <v>2008802.800734619</v>
       </c>
       <c r="N15" t="n">
-        <v>72.12727272727274</v>
+        <v>71.05679522497704</v>
       </c>
       <c r="O15" t="n">
-        <v>24.07399328684158</v>
+        <v>26.40438232006181</v>
       </c>
       <c r="P15" t="n">
-        <v>180.1743961805881</v>
+        <v>179.7010376290892</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.062701316571286</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>64.58257758180359</v>
+        <v>67.01924614917232</v>
       </c>
       <c r="S15" t="n">
-        <v>1730159.632965361</v>
+        <v>1548560.965846393</v>
       </c>
       <c r="T15" t="n">
-        <v>70.30600379439387</v>
+        <v>69.56579898698011</v>
       </c>
       <c r="U15" t="n">
-        <v>26.00565217391304</v>
+        <v>23.69994929634013</v>
       </c>
       <c r="V15" t="n">
-        <v>179.8413043478261</v>
+        <v>181.9869378688367</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.005347593582888</v>
       </c>
       <c r="X15" t="n">
-        <v>66.86782608695653</v>
+        <v>63.77054131333491</v>
       </c>
       <c r="Y15" t="n">
-        <v>1578473.913043478</v>
+        <v>1210949.040138352</v>
       </c>
       <c r="Z15" t="n">
-        <v>69.96913043478261</v>
+        <v>69.73895716455542</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>27.23321678321679</v>
+      </c>
+      <c r="D16" t="n">
+        <v>179.9846153846154</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.055244755244755</v>
+      </c>
+      <c r="F16" t="n">
+        <v>66.32447552447553</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1243762.237762238</v>
+      </c>
+      <c r="H16" t="n">
+        <v>69.24999999999999</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>25.32673159418616</v>
+      </c>
+      <c r="P16" t="n">
+        <v>180.0282591981014</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.065582881395238</v>
+      </c>
+      <c r="R16" t="n">
+        <v>63.12229113593663</v>
+      </c>
+      <c r="S16" t="n">
+        <v>978096.9449809925</v>
+      </c>
+      <c r="T16" t="n">
+        <v>67.4862462413822</v>
+      </c>
+      <c r="U16" t="n">
+        <v>20.42857142857143</v>
+      </c>
+      <c r="V16" t="n">
+        <v>190.8285714285714</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>53.99047619047619</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>245809.5238095238</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.89177350427351</v>
+      </c>
+      <c r="D17" t="n">
+        <v>178.9333333333333</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.237393162393162</v>
+      </c>
+      <c r="F17" t="n">
+        <v>69.07382478632479</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2111908.653846154</v>
+      </c>
+      <c r="H17" t="n">
+        <v>72.68002136752136</v>
+      </c>
+      <c r="I17" t="n">
+        <v>27.95029461279461</v>
+      </c>
+      <c r="J17" t="n">
+        <v>180.9389730639731</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.355765993265993</v>
+      </c>
+      <c r="L17" t="n">
+        <v>72.25223063973063</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4156005.892255893</v>
+      </c>
+      <c r="N17" t="n">
+        <v>74.88489057239057</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.22683843466923</v>
+      </c>
+      <c r="P17" t="n">
+        <v>178.1881626860897</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.09467744597052</v>
+      </c>
+      <c r="R17" t="n">
+        <v>64.07150436637666</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1654372.928225007</v>
+      </c>
+      <c r="T17" t="n">
+        <v>70.12545419528274</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25.30319930495762</v>
+      </c>
+      <c r="V17" t="n">
+        <v>179.407554828247</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.009185932827237</v>
+      </c>
+      <c r="X17" t="n">
+        <v>66.64130965992778</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1675512.968426472</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>72.55957307543385</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.81818181818182</v>
+        <v>25.71515151515151</v>
       </c>
       <c r="D2" t="n">
-        <v>181.6375</v>
+        <v>181.5777777777778</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>68.08484848484848</v>
+        <v>67.96848484848485</v>
       </c>
       <c r="G2" t="n">
-        <v>3378929.924242424</v>
+        <v>3256979.797979798</v>
       </c>
       <c r="H2" t="n">
-        <v>72.04848484848485</v>
+        <v>71.9670707070707</v>
       </c>
       <c r="I2" t="n">
-        <v>26.82326388888889</v>
+        <v>26.74087301587302</v>
       </c>
       <c r="J2" t="n">
-        <v>178.7697916666667</v>
+        <v>179.3992063492063</v>
       </c>
       <c r="K2" t="n">
-        <v>1.177083333333333</v>
+        <v>1.173809523809524</v>
       </c>
       <c r="L2" t="n">
-        <v>69.28194444444445</v>
+        <v>69.20793650793651</v>
       </c>
       <c r="M2" t="n">
-        <v>2437809.027777778</v>
+        <v>2479353.174603175</v>
       </c>
       <c r="N2" t="n">
-        <v>72.42395833333333</v>
+        <v>72.44166666666668</v>
       </c>
       <c r="O2" t="n">
-        <v>23.98889998889999</v>
+        <v>24.10215617715618</v>
       </c>
       <c r="P2" t="n">
-        <v>179.8143384393385</v>
+        <v>179.5005869130869</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>65.21193736818738</v>
+        <v>65.57434648684651</v>
       </c>
       <c r="S2" t="n">
-        <v>2111315.663503163</v>
+        <v>2294799.034299034</v>
       </c>
       <c r="T2" t="n">
-        <v>71.33468961593961</v>
+        <v>71.5803071928072</v>
       </c>
       <c r="U2" t="n">
-        <v>24.66446344842285</v>
+        <v>24.80224394105468</v>
       </c>
       <c r="V2" t="n">
-        <v>177.4474344629156</v>
+        <v>177.7802049080502</v>
       </c>
       <c r="W2" t="n">
-        <v>1.183539801790281</v>
+        <v>1.188331202046036</v>
       </c>
       <c r="X2" t="n">
-        <v>66.9036058716965</v>
+        <v>66.88983528193886</v>
       </c>
       <c r="Y2" t="n">
-        <v>2834091.145833333</v>
+        <v>2760425.595238095</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.34018941815856</v>
+        <v>73.11735933503836</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.26666666666667</v>
+        <v>26.58</v>
       </c>
       <c r="D3" t="n">
-        <v>181.1685185185186</v>
+        <v>181.1822222222223</v>
       </c>
       <c r="E3" t="n">
-        <v>1.053703703703704</v>
+        <v>1.064444444444444</v>
       </c>
       <c r="F3" t="n">
-        <v>67.10740740740739</v>
+        <v>67.1888888888889</v>
       </c>
       <c r="G3" t="n">
-        <v>1762638.888888889</v>
+        <v>1839666.666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>71.24444444444445</v>
+        <v>70.89333333333335</v>
       </c>
       <c r="I3" t="n">
-        <v>25.06700336700337</v>
+        <v>25.17558922558922</v>
       </c>
       <c r="J3" t="n">
-        <v>182.6554292929293</v>
+        <v>182.3321548821549</v>
       </c>
       <c r="K3" t="n">
-        <v>1.212710437710438</v>
+        <v>1.191582491582492</v>
       </c>
       <c r="L3" t="n">
-        <v>66.53160774410775</v>
+        <v>66.94208754208753</v>
       </c>
       <c r="M3" t="n">
-        <v>1983490.109427609</v>
+        <v>2060681.818181818</v>
       </c>
       <c r="N3" t="n">
-        <v>70.77521043771044</v>
+        <v>70.88249158249158</v>
       </c>
       <c r="O3" t="n">
-        <v>26.05484749455338</v>
+        <v>25.79668655868145</v>
       </c>
       <c r="P3" t="n">
-        <v>181.1303376906318</v>
+        <v>180.4664052287582</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.074945533769063</v>
+        <v>1.073796533105996</v>
       </c>
       <c r="R3" t="n">
-        <v>65.87941176470589</v>
+        <v>66.03312020460359</v>
       </c>
       <c r="S3" t="n">
-        <v>1225298.202614379</v>
+        <v>1435218.456947997</v>
       </c>
       <c r="T3" t="n">
-        <v>70.50310457516339</v>
+        <v>71.12160272804775</v>
       </c>
       <c r="U3" t="n">
-        <v>23.62749766573296</v>
+        <v>23.80319211017741</v>
       </c>
       <c r="V3" t="n">
-        <v>181.8678026766262</v>
+        <v>182.152293417367</v>
       </c>
       <c r="W3" t="n">
         <v>1.019607843137255</v>
       </c>
       <c r="X3" t="n">
-        <v>62.32547463429817</v>
+        <v>62.80070611577964</v>
       </c>
       <c r="Y3" t="n">
-        <v>1080415.305010893</v>
+        <v>1130583.129084967</v>
       </c>
       <c r="Z3" t="n">
-        <v>68.98210395269219</v>
+        <v>69.09622432306256</v>
       </c>
     </row>
     <row r="4">
@@ -729,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>22.16666666666667</v>
+        <v>22.26</v>
       </c>
       <c r="D4" t="n">
-        <v>180.2</v>
+        <v>180.3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>65.73333333333333</v>
+        <v>65.67999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2086166.666666667</v>
+        <v>2039000</v>
       </c>
       <c r="H4" t="n">
-        <v>73.56666666666666</v>
+        <v>73.42</v>
       </c>
       <c r="I4" t="n">
-        <v>27.46233766233766</v>
+        <v>27.49350649350649</v>
       </c>
       <c r="J4" t="n">
-        <v>180.9974025974026</v>
+        <v>180.7922077922078</v>
       </c>
       <c r="K4" t="n">
-        <v>1.054545454545454</v>
+        <v>1.051948051948052</v>
       </c>
       <c r="L4" t="n">
-        <v>65.9064935064935</v>
+        <v>65.98701298701299</v>
       </c>
       <c r="M4" t="n">
-        <v>1204441.558441559</v>
+        <v>1200909.090909091</v>
       </c>
       <c r="N4" t="n">
-        <v>68.75844155844156</v>
+        <v>68.75324675324676</v>
       </c>
       <c r="O4" t="n">
-        <v>23.27406905744754</v>
+        <v>23.35241228070175</v>
       </c>
       <c r="P4" t="n">
-        <v>181.6231295149639</v>
+        <v>181.4065789473684</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>63.41337074303406</v>
+        <v>63.35486842105263</v>
       </c>
       <c r="S4" t="n">
-        <v>1260498.803176241</v>
+        <v>1277069.152046784</v>
       </c>
       <c r="T4" t="n">
-        <v>71.32203087375301</v>
+        <v>71.19820175438596</v>
       </c>
       <c r="U4" t="n">
-        <v>26.15272271588061</v>
+        <v>26.20622356285972</v>
       </c>
       <c r="V4" t="n">
-        <v>179.7734954268789</v>
+        <v>179.5871937749512</v>
       </c>
       <c r="W4" t="n">
-        <v>1.087012173290369</v>
+        <v>1.084461152882206</v>
       </c>
       <c r="X4" t="n">
-        <v>64.29777121374866</v>
+        <v>64.37136764836994</v>
       </c>
       <c r="Y4" t="n">
-        <v>1105770.949288806</v>
+        <v>1103541.125541126</v>
       </c>
       <c r="Z4" t="n">
-        <v>68.04186358754029</v>
+        <v>68.03731611637791</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>71.68181818181817</v>
       </c>
       <c r="I5" t="n">
-        <v>27.06646464646465</v>
+        <v>27.4080808080808</v>
       </c>
       <c r="J5" t="n">
-        <v>183.3460606060606</v>
+        <v>183.0575757575758</v>
       </c>
       <c r="K5" t="n">
-        <v>1.100404040404041</v>
+        <v>1.100505050505051</v>
       </c>
       <c r="L5" t="n">
-        <v>67.13616161616162</v>
+        <v>67.32020202020202</v>
       </c>
       <c r="M5" t="n">
-        <v>1354939.393939394</v>
+        <v>1364924.242424242</v>
       </c>
       <c r="N5" t="n">
-        <v>70.44343434343435</v>
+        <v>70.27929292929292</v>
       </c>
       <c r="O5" t="n">
         <v>24.87184560132215</v>
@@ -865,22 +865,22 @@
         <v>69.16638062547675</v>
       </c>
       <c r="U5" t="n">
-        <v>22.70494987468672</v>
+        <v>22.98535401002506</v>
       </c>
       <c r="V5" t="n">
-        <v>183.442888471178</v>
+        <v>183.0119439223058</v>
       </c>
       <c r="W5" t="n">
-        <v>1.010526315789474</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="X5" t="n">
-        <v>60.95191102756892</v>
+        <v>61.81488878446115</v>
       </c>
       <c r="Y5" t="n">
-        <v>895474.9373433584</v>
+        <v>995697.8383458648</v>
       </c>
       <c r="Z5" t="n">
-        <v>69.55391604010025</v>
+        <v>70.15072838345864</v>
       </c>
     </row>
     <row r="6">
@@ -911,22 +911,22 @@
         <v>71.60727272727273</v>
       </c>
       <c r="I6" t="n">
-        <v>28.46885521885522</v>
+        <v>28.60303030303031</v>
       </c>
       <c r="J6" t="n">
-        <v>181.1343434343435</v>
+        <v>180.7015151515151</v>
       </c>
       <c r="K6" t="n">
-        <v>1.401346801346801</v>
+        <v>1.387878787878788</v>
       </c>
       <c r="L6" t="n">
-        <v>72.17861952861954</v>
+        <v>72.35757575757576</v>
       </c>
       <c r="M6" t="n">
-        <v>4009036.195286195</v>
+        <v>4027651.515151516</v>
       </c>
       <c r="N6" t="n">
-        <v>74.70404040404041</v>
+        <v>74.58939393939393</v>
       </c>
       <c r="O6" t="n">
         <v>25.52729315583536</v>
@@ -947,22 +947,22 @@
         <v>68.50703106214614</v>
       </c>
       <c r="U6" t="n">
-        <v>24.63389780154486</v>
+        <v>25.08525167642815</v>
       </c>
       <c r="V6" t="n">
-        <v>179.4720885323826</v>
+        <v>179.6502504031916</v>
       </c>
       <c r="W6" t="n">
-        <v>1.008333333333333</v>
+        <v>1.055952380952381</v>
       </c>
       <c r="X6" t="n">
-        <v>67.11437908496733</v>
+        <v>67.4250233426704</v>
       </c>
       <c r="Y6" t="n">
-        <v>1928738.859180036</v>
+        <v>2096077.794754266</v>
       </c>
       <c r="Z6" t="n">
-        <v>73.82133095662508</v>
+        <v>73.7279602750191</v>
       </c>
     </row>
     <row r="7">
@@ -975,28 +975,28 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.77818181818181</v>
+        <v>25.3810606060606</v>
       </c>
       <c r="D7" t="n">
-        <v>176.4581818181818</v>
+        <v>176.6742424242424</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>68.9290909090909</v>
+        <v>68.99747474747474</v>
       </c>
       <c r="G7" t="n">
-        <v>2707045.454545455</v>
+        <v>2828598.484848485</v>
       </c>
       <c r="H7" t="n">
-        <v>71.7</v>
+        <v>72.10277777777777</v>
       </c>
       <c r="I7" t="n">
         <v>25.98181818181818</v>
       </c>
       <c r="J7" t="n">
-        <v>181.9845598845599</v>
+        <v>182.153391053391</v>
       </c>
       <c r="K7" t="n">
         <v>1.055844155844156</v>
@@ -1011,28 +1011,28 @@
         <v>69.13477633477632</v>
       </c>
       <c r="O7" t="n">
-        <v>25.25575098814229</v>
+        <v>25.29416996047431</v>
       </c>
       <c r="P7" t="n">
-        <v>178.3410869565217</v>
+        <v>178.5049407114624</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>65.19758234519104</v>
+        <v>65.23908102766799</v>
       </c>
       <c r="S7" t="n">
-        <v>1288521.739130435</v>
+        <v>1289512.104743083</v>
       </c>
       <c r="T7" t="n">
-        <v>69.47237154150199</v>
+        <v>69.50578063241107</v>
       </c>
       <c r="U7" t="n">
         <v>25.37236188733867</v>
       </c>
       <c r="V7" t="n">
-        <v>180.343819082657</v>
+        <v>180.4282298804689</v>
       </c>
       <c r="W7" t="n">
         <v>1.035211811997526</v>
@@ -1045,6 +1045,1072 @@
       </c>
       <c r="Z7" t="n">
         <v>69.14688461509004</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27.12424242424242</v>
+      </c>
+      <c r="D8" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.078787878787879</v>
+      </c>
+      <c r="F8" t="n">
+        <v>66.9530303030303</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1408492.424242424</v>
+      </c>
+      <c r="H8" t="n">
+        <v>69.66515151515152</v>
+      </c>
+      <c r="I8" t="n">
+        <v>27.39848484848485</v>
+      </c>
+      <c r="J8" t="n">
+        <v>183.430303030303</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.13939393939394</v>
+      </c>
+      <c r="L8" t="n">
+        <v>68.03030303030305</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3074621.212121212</v>
+      </c>
+      <c r="N8" t="n">
+        <v>69.62575757575758</v>
+      </c>
+      <c r="O8" t="n">
+        <v>25.59707602339181</v>
+      </c>
+      <c r="P8" t="n">
+        <v>179.3770467836257</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>65.30109649122808</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1454587.902046784</v>
+      </c>
+      <c r="T8" t="n">
+        <v>70.44630847953216</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.06470192958953</v>
+      </c>
+      <c r="V8" t="n">
+        <v>183.2764525337213</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.014492753623188</v>
+      </c>
+      <c r="X8" t="n">
+        <v>63.34859890561869</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>872897.4709258227</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>65.62857062733561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>23.77979797979798</v>
+      </c>
+      <c r="D9" t="n">
+        <v>179.5129292929293</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.074545454545455</v>
+      </c>
+      <c r="F9" t="n">
+        <v>66.22161616161615</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1430424.242424242</v>
+      </c>
+      <c r="H9" t="n">
+        <v>72.22888888888887</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="J9" t="n">
+        <v>180.5636363636364</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>68.25454545454545</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2175000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="O9" t="n">
+        <v>23.54262360446571</v>
+      </c>
+      <c r="P9" t="n">
+        <v>178.3436602870813</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.087041467304625</v>
+      </c>
+      <c r="R9" t="n">
+        <v>66.00043859649124</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1544188.397129187</v>
+      </c>
+      <c r="T9" t="n">
+        <v>72.04358054226475</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.29959477862291</v>
+      </c>
+      <c r="V9" t="n">
+        <v>182.9713621416946</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>65.41922144351813</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1921685.820573288</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>70.70330820075066</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>27.4080808080808</v>
+      </c>
+      <c r="D10" t="n">
+        <v>183.0575757575758</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.100505050505051</v>
+      </c>
+      <c r="F10" t="n">
+        <v>67.32020202020202</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1364924.242424242</v>
+      </c>
+      <c r="H10" t="n">
+        <v>70.27929292929292</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="J10" t="n">
+        <v>182.3861111111111</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.022222222222222</v>
+      </c>
+      <c r="L10" t="n">
+        <v>66.08611111111111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1593819.444444444</v>
+      </c>
+      <c r="N10" t="n">
+        <v>73.26388888888889</v>
+      </c>
+      <c r="O10" t="n">
+        <v>22.98535401002506</v>
+      </c>
+      <c r="P10" t="n">
+        <v>183.0119439223058</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.013157894736842</v>
+      </c>
+      <c r="R10" t="n">
+        <v>61.81488878446115</v>
+      </c>
+      <c r="S10" t="n">
+        <v>995697.8383458648</v>
+      </c>
+      <c r="T10" t="n">
+        <v>70.15072838345864</v>
+      </c>
+      <c r="U10" t="n">
+        <v>22.72417675204053</v>
+      </c>
+      <c r="V10" t="n">
+        <v>179.979083309879</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.099299043062201</v>
+      </c>
+      <c r="X10" t="n">
+        <v>62.95826175063327</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1411628.570925978</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>72.03322628764424</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24.41818181818182</v>
+      </c>
+      <c r="D11" t="n">
+        <v>181.9072727272727</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67.47999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2451763.636363636</v>
+      </c>
+      <c r="H11" t="n">
+        <v>72.60909090909091</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25.71515151515151</v>
+      </c>
+      <c r="J11" t="n">
+        <v>181.5777777777778</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>67.96848484848485</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3256979.797979798</v>
+      </c>
+      <c r="N11" t="n">
+        <v>71.9670707070707</v>
+      </c>
+      <c r="O11" t="n">
+        <v>24.24963768115942</v>
+      </c>
+      <c r="P11" t="n">
+        <v>181.0010869565218</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>62.5018115942029</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2158038.043478261</v>
+      </c>
+      <c r="T11" t="n">
+        <v>67.71992753623189</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24.10215617715618</v>
+      </c>
+      <c r="V11" t="n">
+        <v>179.5005869130869</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>65.57434648684651</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2294799.034299034</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>71.5803071928072</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.08863636363637</v>
+      </c>
+      <c r="D12" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.481818181818182</v>
+      </c>
+      <c r="F12" t="n">
+        <v>71.58636363636363</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4704659.090909091</v>
+      </c>
+      <c r="H12" t="n">
+        <v>76.64772727272727</v>
+      </c>
+      <c r="I12" t="n">
+        <v>26.81636363636363</v>
+      </c>
+      <c r="J12" t="n">
+        <v>183.5054545454545</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.130909090909091</v>
+      </c>
+      <c r="L12" t="n">
+        <v>71.67999999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3297909.090909091</v>
+      </c>
+      <c r="N12" t="n">
+        <v>74.01636363636364</v>
+      </c>
+      <c r="O12" t="n">
+        <v>22.93650793650794</v>
+      </c>
+      <c r="P12" t="n">
+        <v>183.6582341269841</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.058035714285714</v>
+      </c>
+      <c r="R12" t="n">
+        <v>67.1889880952381</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2308774.801587301</v>
+      </c>
+      <c r="T12" t="n">
+        <v>75.2936507936508</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.64467787114846</v>
+      </c>
+      <c r="V12" t="n">
+        <v>183.4112324929972</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.107002801120448</v>
+      </c>
+      <c r="X12" t="n">
+        <v>64.26168067226891</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1267851.820728291</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>70.42638655462186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.22000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>179.56</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F13" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2493500</v>
+      </c>
+      <c r="H13" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="J13" t="n">
+        <v>181.1822222222223</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.064444444444444</v>
+      </c>
+      <c r="L13" t="n">
+        <v>67.1888888888889</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1839666.666666667</v>
+      </c>
+      <c r="N13" t="n">
+        <v>70.89333333333335</v>
+      </c>
+      <c r="O13" t="n">
+        <v>26.40372670807453</v>
+      </c>
+      <c r="P13" t="n">
+        <v>180.0136645962733</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.363975155279503</v>
+      </c>
+      <c r="R13" t="n">
+        <v>67.33540372670807</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3346997.929606625</v>
+      </c>
+      <c r="T13" t="n">
+        <v>71.22981366459626</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.79668655868145</v>
+      </c>
+      <c r="V13" t="n">
+        <v>180.4664052287582</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.073796533105996</v>
+      </c>
+      <c r="X13" t="n">
+        <v>66.03312020460359</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1435218.456947997</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>71.12160272804775</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.54080808080808</v>
+      </c>
+      <c r="D14" t="n">
+        <v>181.0583838383838</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.259393939393939</v>
+      </c>
+      <c r="F14" t="n">
+        <v>67.24242424242425</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2580970.707070707</v>
+      </c>
+      <c r="H14" t="n">
+        <v>69.31171717171716</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="J14" t="n">
+        <v>181.4822222222222</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.204444444444444</v>
+      </c>
+      <c r="L14" t="n">
+        <v>67.04666666666667</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2133166.666666667</v>
+      </c>
+      <c r="N14" t="n">
+        <v>68.56888888888889</v>
+      </c>
+      <c r="O14" t="n">
+        <v>24.24339826839827</v>
+      </c>
+      <c r="P14" t="n">
+        <v>181.7162878787879</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.194318181818182</v>
+      </c>
+      <c r="R14" t="n">
+        <v>63.82202380952381</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1859379.87012987</v>
+      </c>
+      <c r="T14" t="n">
+        <v>68.54431818181817</v>
+      </c>
+      <c r="U14" t="n">
+        <v>28.31732040905954</v>
+      </c>
+      <c r="V14" t="n">
+        <v>179.8015672250455</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.190493757450279</v>
+      </c>
+      <c r="X14" t="n">
+        <v>66.54496455235585</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1245346.87245122</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>67.8298795407491</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>26.25757575757576</v>
+      </c>
+      <c r="D15" t="n">
+        <v>182.8484848484848</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="F15" t="n">
+        <v>68.53030303030303</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2365151.515151516</v>
+      </c>
+      <c r="H15" t="n">
+        <v>71.68181818181817</v>
+      </c>
+      <c r="I15" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>65.67999999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2039000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>73.42</v>
+      </c>
+      <c r="O15" t="n">
+        <v>24.87184560132215</v>
+      </c>
+      <c r="P15" t="n">
+        <v>180.9194555682685</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.006944444444444</v>
+      </c>
+      <c r="R15" t="n">
+        <v>64.20262840071193</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1107212.329964404</v>
+      </c>
+      <c r="T15" t="n">
+        <v>69.16638062547675</v>
+      </c>
+      <c r="U15" t="n">
+        <v>23.35241228070175</v>
+      </c>
+      <c r="V15" t="n">
+        <v>181.4065789473684</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>63.35486842105263</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1277069.152046784</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>71.19820175438596</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>27.23272727272727</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.4945454545455</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.192727272727273</v>
+      </c>
+      <c r="F16" t="n">
+        <v>68.55454545454546</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2028936.363636364</v>
+      </c>
+      <c r="H16" t="n">
+        <v>71.60727272727273</v>
+      </c>
+      <c r="I16" t="n">
+        <v>24.98686868686869</v>
+      </c>
+      <c r="J16" t="n">
+        <v>179.5739393939394</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>66.33656565656565</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1722348.484848485</v>
+      </c>
+      <c r="N16" t="n">
+        <v>71.9979797979798</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25.52729315583536</v>
+      </c>
+      <c r="P16" t="n">
+        <v>178.0795901370581</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>65.21619122565414</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1096387.178394212</v>
+      </c>
+      <c r="T16" t="n">
+        <v>68.50703106214614</v>
+      </c>
+      <c r="U16" t="n">
+        <v>26.40285714285715</v>
+      </c>
+      <c r="V16" t="n">
+        <v>179.4809523809524</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>66.09301587301586</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1449616.26984127</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>69.95849206349207</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25.17558922558922</v>
+      </c>
+      <c r="D17" t="n">
+        <v>182.3321548821549</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.191582491582492</v>
+      </c>
+      <c r="F17" t="n">
+        <v>66.94208754208753</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2060681.818181818</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70.88249158249158</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25.12727272727273</v>
+      </c>
+      <c r="J17" t="n">
+        <v>181.1287878787878</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>65.37272727272727</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1297598.484848485</v>
+      </c>
+      <c r="N17" t="n">
+        <v>70.18939393939394</v>
+      </c>
+      <c r="O17" t="n">
+        <v>23.80319211017741</v>
+      </c>
+      <c r="P17" t="n">
+        <v>182.152293417367</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.019607843137255</v>
+      </c>
+      <c r="R17" t="n">
+        <v>62.80070611577964</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1130583.129084967</v>
+      </c>
+      <c r="T17" t="n">
+        <v>69.09622432306256</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25.33894478844169</v>
+      </c>
+      <c r="V17" t="n">
+        <v>177.8566821465429</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>64.80256707946337</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1459503.515221878</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>69.66224845201238</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.27111111111111</v>
+      </c>
+      <c r="D18" t="n">
+        <v>179.8355555555555</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>64.88444444444444</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1324855.555555556</v>
+      </c>
+      <c r="H18" t="n">
+        <v>69.89777777777778</v>
+      </c>
+      <c r="I18" t="n">
+        <v>26.64727272727272</v>
+      </c>
+      <c r="J18" t="n">
+        <v>177.6054545454545</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>69.10363636363635</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2108863.636363636</v>
+      </c>
+      <c r="N18" t="n">
+        <v>71.87272727272727</v>
+      </c>
+      <c r="O18" t="n">
+        <v>21.35765480895916</v>
+      </c>
+      <c r="P18" t="n">
+        <v>180.5926482213439</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>58.3937417654809</v>
+      </c>
+      <c r="S18" t="n">
+        <v>610425.1646903821</v>
+      </c>
+      <c r="T18" t="n">
+        <v>68.52461133069828</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25.45601449275362</v>
+      </c>
+      <c r="V18" t="n">
+        <v>181.6361231884058</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>66.73724637681158</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1481006.884057971</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>69.84210144927536</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26.43333333333333</v>
+      </c>
+      <c r="D19" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>70.63333333333334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3900833.333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>74.05000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>28.60303030303031</v>
+      </c>
+      <c r="J19" t="n">
+        <v>180.7015151515151</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.387878787878788</v>
+      </c>
+      <c r="L19" t="n">
+        <v>72.35757575757576</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4027651.515151516</v>
+      </c>
+      <c r="N19" t="n">
+        <v>74.58939393939393</v>
+      </c>
+      <c r="O19" t="n">
+        <v>24.49826824004456</v>
+      </c>
+      <c r="P19" t="n">
+        <v>180.1154274575327</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.105054302422724</v>
+      </c>
+      <c r="R19" t="n">
+        <v>64.77993595098859</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1900719.028473963</v>
+      </c>
+      <c r="T19" t="n">
+        <v>70.15235136452242</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.08525167642815</v>
+      </c>
+      <c r="V19" t="n">
+        <v>179.6502504031916</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.055952380952381</v>
+      </c>
+      <c r="X19" t="n">
+        <v>67.4250233426704</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2096077.794754266</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>73.7279602750191</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>25.3810606060606</v>
+      </c>
+      <c r="D20" t="n">
+        <v>176.6742424242424</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>68.99747474747474</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2828598.484848485</v>
+      </c>
+      <c r="H20" t="n">
+        <v>72.10277777777777</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>179.5333333333333</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>68.85000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2990166.666666667</v>
+      </c>
+      <c r="N20" t="n">
+        <v>71.73333333333333</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25.29416996047431</v>
+      </c>
+      <c r="P20" t="n">
+        <v>178.5049407114624</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>65.23908102766799</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1289512.104743083</v>
+      </c>
+      <c r="T20" t="n">
+        <v>69.50578063241107</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.38565217391304</v>
+      </c>
+      <c r="V20" t="n">
+        <v>180.1132125603865</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>65.94187747035573</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1450997.51866491</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>69.38378238910848</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,1559 +558,2215 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>A3m1Vera</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.71515151515151</v>
+        <v>27.72909090909091</v>
       </c>
       <c r="D2" t="n">
-        <v>181.5777777777778</v>
+        <v>179.86</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.094545454545454</v>
       </c>
       <c r="F2" t="n">
-        <v>67.96848484848485</v>
+        <v>67.26363636363638</v>
       </c>
       <c r="G2" t="n">
-        <v>3256979.797979798</v>
+        <v>1443190.909090909</v>
       </c>
       <c r="H2" t="n">
-        <v>71.9670707070707</v>
+        <v>69.27818181818182</v>
       </c>
       <c r="I2" t="n">
-        <v>26.74087301587302</v>
+        <v>27.55090909090909</v>
       </c>
       <c r="J2" t="n">
-        <v>179.3992063492063</v>
+        <v>183.3709090909091</v>
       </c>
       <c r="K2" t="n">
-        <v>1.173809523809524</v>
+        <v>1.130909090909091</v>
       </c>
       <c r="L2" t="n">
-        <v>69.20793650793651</v>
+        <v>68.05454545454546</v>
       </c>
       <c r="M2" t="n">
-        <v>2479353.174603175</v>
+        <v>3035363.636363636</v>
       </c>
       <c r="N2" t="n">
-        <v>72.44166666666668</v>
+        <v>69.51454545454546</v>
       </c>
       <c r="O2" t="n">
-        <v>24.10215617715618</v>
+        <v>25.68491228070176</v>
       </c>
       <c r="P2" t="n">
-        <v>179.5005869130869</v>
+        <v>179.2208771929825</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>65.57434648684651</v>
+        <v>65.54026315789474</v>
       </c>
       <c r="S2" t="n">
-        <v>2294799.034299034</v>
+        <v>1578663.377192982</v>
       </c>
       <c r="T2" t="n">
-        <v>71.5803071928072</v>
+        <v>70.2934649122807</v>
       </c>
       <c r="U2" t="n">
-        <v>24.80224394105468</v>
+        <v>26.8515553589857</v>
       </c>
       <c r="V2" t="n">
-        <v>177.7802049080502</v>
+        <v>183.088264779596</v>
       </c>
       <c r="W2" t="n">
-        <v>1.188331202046036</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>66.88983528193886</v>
+        <v>62.96614477369896</v>
       </c>
       <c r="Y2" t="n">
-        <v>2760425.595238095</v>
+        <v>696129.1390240307</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.11735933503836</v>
+        <v>65.4760238832375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>8lOY3V6E</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.58</v>
+        <v>23.77979797979798</v>
       </c>
       <c r="D3" t="n">
-        <v>181.1822222222223</v>
+        <v>179.5129292929293</v>
       </c>
       <c r="E3" t="n">
-        <v>1.064444444444444</v>
+        <v>1.074545454545455</v>
       </c>
       <c r="F3" t="n">
-        <v>67.1888888888889</v>
+        <v>66.22161616161615</v>
       </c>
       <c r="G3" t="n">
-        <v>1839666.666666667</v>
+        <v>1430424.242424242</v>
       </c>
       <c r="H3" t="n">
-        <v>70.89333333333335</v>
+        <v>72.22888888888887</v>
       </c>
       <c r="I3" t="n">
-        <v>25.17558922558922</v>
+        <v>26.36363636363636</v>
       </c>
       <c r="J3" t="n">
-        <v>182.3321548821549</v>
+        <v>180.5636363636364</v>
       </c>
       <c r="K3" t="n">
-        <v>1.191582491582492</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>66.94208754208753</v>
+        <v>68.25454545454545</v>
       </c>
       <c r="M3" t="n">
-        <v>2060681.818181818</v>
+        <v>2175000</v>
       </c>
       <c r="N3" t="n">
-        <v>70.88249158249158</v>
+        <v>72.54545454545455</v>
       </c>
       <c r="O3" t="n">
-        <v>25.79668655868145</v>
+        <v>23.54262360446571</v>
       </c>
       <c r="P3" t="n">
-        <v>180.4664052287582</v>
+        <v>178.3436602870813</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.073796533105996</v>
+        <v>1.087041467304625</v>
       </c>
       <c r="R3" t="n">
-        <v>66.03312020460359</v>
+        <v>66.00043859649124</v>
       </c>
       <c r="S3" t="n">
-        <v>1435218.456947997</v>
+        <v>1544188.397129187</v>
       </c>
       <c r="T3" t="n">
-        <v>71.12160272804775</v>
+        <v>72.04358054226475</v>
       </c>
       <c r="U3" t="n">
-        <v>23.80319211017741</v>
+        <v>25.29959477862291</v>
       </c>
       <c r="V3" t="n">
-        <v>182.152293417367</v>
+        <v>182.9713621416946</v>
       </c>
       <c r="W3" t="n">
-        <v>1.019607843137255</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>62.80070611577964</v>
+        <v>65.41922144351813</v>
       </c>
       <c r="Y3" t="n">
-        <v>1130583.129084967</v>
+        <v>1921685.820573288</v>
       </c>
       <c r="Z3" t="n">
-        <v>69.09622432306256</v>
+        <v>70.70330820075066</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>ITj9TZCB</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>22.26</v>
+        <v>27.46646464646465</v>
       </c>
       <c r="D4" t="n">
-        <v>180.3</v>
+        <v>183.1260606060606</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.100404040404041</v>
       </c>
       <c r="F4" t="n">
-        <v>65.67999999999999</v>
+        <v>67.3561616161616</v>
       </c>
       <c r="G4" t="n">
-        <v>2039000</v>
+        <v>1369939.393939394</v>
       </c>
       <c r="H4" t="n">
-        <v>73.42</v>
+        <v>70.18343434343434</v>
       </c>
       <c r="I4" t="n">
-        <v>27.49350649350649</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="J4" t="n">
-        <v>180.7922077922078</v>
+        <v>182.3861111111111</v>
       </c>
       <c r="K4" t="n">
-        <v>1.051948051948052</v>
+        <v>1.022222222222222</v>
       </c>
       <c r="L4" t="n">
-        <v>65.98701298701299</v>
+        <v>66.08611111111111</v>
       </c>
       <c r="M4" t="n">
-        <v>1200909.090909091</v>
+        <v>1593819.444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>68.75324675324676</v>
+        <v>73.26388888888889</v>
       </c>
       <c r="O4" t="n">
-        <v>23.35241228070175</v>
+        <v>23.27717209690894</v>
       </c>
       <c r="P4" t="n">
-        <v>181.4065789473684</v>
+        <v>182.7984440267335</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>1.021637426900585</v>
       </c>
       <c r="R4" t="n">
-        <v>63.35486842105263</v>
+        <v>61.89635547201336</v>
       </c>
       <c r="S4" t="n">
-        <v>1277069.152046784</v>
+        <v>995113.8262322474</v>
       </c>
       <c r="T4" t="n">
-        <v>71.19820175438596</v>
+        <v>69.84280492898914</v>
       </c>
       <c r="U4" t="n">
-        <v>26.20622356285972</v>
+        <v>22.72417675204053</v>
       </c>
       <c r="V4" t="n">
-        <v>179.5871937749512</v>
+        <v>179.979083309879</v>
       </c>
       <c r="W4" t="n">
-        <v>1.084461152882206</v>
+        <v>1.099299043062201</v>
       </c>
       <c r="X4" t="n">
-        <v>64.37136764836994</v>
+        <v>62.95826175063327</v>
       </c>
       <c r="Y4" t="n">
-        <v>1103541.125541126</v>
+        <v>1411628.570925978</v>
       </c>
       <c r="Z4" t="n">
-        <v>68.03731611637791</v>
+        <v>72.03322628764424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>lfn5UFc5</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>26.25757575757576</v>
+        <v>24.41818181818182</v>
       </c>
       <c r="D5" t="n">
-        <v>182.8484848484848</v>
+        <v>181.9072727272727</v>
       </c>
       <c r="E5" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>68.53030303030303</v>
+        <v>67.47999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2365151.515151516</v>
+        <v>2451763.636363636</v>
       </c>
       <c r="H5" t="n">
-        <v>71.68181818181817</v>
+        <v>72.60909090909091</v>
       </c>
       <c r="I5" t="n">
-        <v>27.4080808080808</v>
+        <v>25.68855218855219</v>
       </c>
       <c r="J5" t="n">
-        <v>183.0575757575758</v>
+        <v>181.3518518518518</v>
       </c>
       <c r="K5" t="n">
-        <v>1.100505050505051</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>67.32020202020202</v>
+        <v>67.75151515151516</v>
       </c>
       <c r="M5" t="n">
-        <v>1364924.242424242</v>
+        <v>3043779.461279461</v>
       </c>
       <c r="N5" t="n">
-        <v>70.27929292929292</v>
+        <v>71.8429292929293</v>
       </c>
       <c r="O5" t="n">
-        <v>24.87184560132215</v>
+        <v>24.24963768115942</v>
       </c>
       <c r="P5" t="n">
-        <v>180.9194555682685</v>
+        <v>181.0010869565218</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.006944444444444</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>64.20262840071193</v>
+        <v>62.5018115942029</v>
       </c>
       <c r="S5" t="n">
-        <v>1107212.329964404</v>
+        <v>2158038.043478261</v>
       </c>
       <c r="T5" t="n">
-        <v>69.16638062547675</v>
+        <v>67.71992753623189</v>
       </c>
       <c r="U5" t="n">
-        <v>22.98535401002506</v>
+        <v>24.40804681429681</v>
       </c>
       <c r="V5" t="n">
-        <v>183.0119439223058</v>
+        <v>179.8859057609058</v>
       </c>
       <c r="W5" t="n">
-        <v>1.013157894736842</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>61.81488878446115</v>
+        <v>65.70778873903875</v>
       </c>
       <c r="Y5" t="n">
-        <v>995697.8383458648</v>
+        <v>2131863.778582529</v>
       </c>
       <c r="Z5" t="n">
-        <v>70.15072838345864</v>
+        <v>71.306505994006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>dKkDSgSH</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>27.23272727272727</v>
+        <v>25.08863636363637</v>
       </c>
       <c r="D6" t="n">
-        <v>181.4945454545455</v>
+        <v>183.75</v>
       </c>
       <c r="E6" t="n">
-        <v>1.192727272727273</v>
+        <v>1.481818181818182</v>
       </c>
       <c r="F6" t="n">
-        <v>68.55454545454546</v>
+        <v>71.58636363636363</v>
       </c>
       <c r="G6" t="n">
-        <v>2028936.363636364</v>
+        <v>4704659.090909091</v>
       </c>
       <c r="H6" t="n">
-        <v>71.60727272727273</v>
+        <v>76.64772727272727</v>
       </c>
       <c r="I6" t="n">
-        <v>28.60303030303031</v>
+        <v>26.81636363636363</v>
       </c>
       <c r="J6" t="n">
-        <v>180.7015151515151</v>
+        <v>183.5054545454545</v>
       </c>
       <c r="K6" t="n">
-        <v>1.387878787878788</v>
+        <v>1.130909090909091</v>
       </c>
       <c r="L6" t="n">
-        <v>72.35757575757576</v>
+        <v>71.67999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>4027651.515151516</v>
+        <v>3297909.090909091</v>
       </c>
       <c r="N6" t="n">
-        <v>74.58939393939393</v>
+        <v>74.01636363636364</v>
       </c>
       <c r="O6" t="n">
-        <v>25.52729315583536</v>
+        <v>22.93650793650794</v>
       </c>
       <c r="P6" t="n">
-        <v>178.0795901370581</v>
+        <v>183.6582341269841</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>1.058035714285714</v>
       </c>
       <c r="R6" t="n">
-        <v>65.21619122565414</v>
+        <v>67.1889880952381</v>
       </c>
       <c r="S6" t="n">
-        <v>1096387.178394212</v>
+        <v>2308774.801587301</v>
       </c>
       <c r="T6" t="n">
-        <v>68.50703106214614</v>
+        <v>75.2936507936508</v>
       </c>
       <c r="U6" t="n">
-        <v>25.08525167642815</v>
+        <v>24.64467787114846</v>
       </c>
       <c r="V6" t="n">
-        <v>179.6502504031916</v>
+        <v>183.4112324929972</v>
       </c>
       <c r="W6" t="n">
-        <v>1.055952380952381</v>
+        <v>1.107002801120448</v>
       </c>
       <c r="X6" t="n">
-        <v>67.4250233426704</v>
+        <v>64.26168067226891</v>
       </c>
       <c r="Y6" t="n">
-        <v>2096077.794754266</v>
+        <v>1267851.820728291</v>
       </c>
       <c r="Z6" t="n">
-        <v>73.7279602750191</v>
+        <v>70.42638655462186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>vquIRDsO</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.3810606060606</v>
+        <v>26.22000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>176.6742424242424</v>
+        <v>179.56</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="F7" t="n">
-        <v>68.99747474747474</v>
+        <v>69.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2828598.484848485</v>
+        <v>2493500</v>
       </c>
       <c r="H7" t="n">
-        <v>72.10277777777777</v>
+        <v>72.66</v>
       </c>
       <c r="I7" t="n">
-        <v>25.98181818181818</v>
+        <v>26.50185185185185</v>
       </c>
       <c r="J7" t="n">
-        <v>182.153391053391</v>
+        <v>181.1148148148148</v>
       </c>
       <c r="K7" t="n">
-        <v>1.055844155844156</v>
+        <v>1.072222222222222</v>
       </c>
       <c r="L7" t="n">
-        <v>65.45425685425685</v>
+        <v>67.43518518518518</v>
       </c>
       <c r="M7" t="n">
-        <v>1634491.341991342</v>
+        <v>2105740.740740741</v>
       </c>
       <c r="N7" t="n">
-        <v>69.13477633477632</v>
+        <v>71.15185185185186</v>
       </c>
       <c r="O7" t="n">
-        <v>25.29416996047431</v>
+        <v>26.40372670807453</v>
       </c>
       <c r="P7" t="n">
-        <v>178.5049407114624</v>
+        <v>180.0136645962733</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>1.363975155279503</v>
       </c>
       <c r="R7" t="n">
-        <v>65.23908102766799</v>
+        <v>67.33540372670807</v>
       </c>
       <c r="S7" t="n">
-        <v>1289512.104743083</v>
+        <v>3346997.929606625</v>
       </c>
       <c r="T7" t="n">
-        <v>69.50578063241107</v>
+        <v>71.22981366459626</v>
       </c>
       <c r="U7" t="n">
-        <v>25.37236188733867</v>
+        <v>26.10438165604406</v>
       </c>
       <c r="V7" t="n">
-        <v>180.4282298804689</v>
+        <v>180.2577186430127</v>
       </c>
       <c r="W7" t="n">
-        <v>1.035211811997526</v>
+        <v>1.073401872826425</v>
       </c>
       <c r="X7" t="n">
-        <v>64.30395636723588</v>
+        <v>66.2418858847887</v>
       </c>
       <c r="Y7" t="n">
-        <v>2116914.754298849</v>
+        <v>1429646.33317095</v>
       </c>
       <c r="Z7" t="n">
-        <v>69.14688461509004</v>
+        <v>70.77990703527787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>jDDw3kMK</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.12424242424242</v>
+        <v>27.54080808080808</v>
       </c>
       <c r="D8" t="n">
-        <v>179.75</v>
+        <v>181.0583838383838</v>
       </c>
       <c r="E8" t="n">
-        <v>1.078787878787879</v>
+        <v>1.259393939393939</v>
       </c>
       <c r="F8" t="n">
-        <v>66.9530303030303</v>
+        <v>67.24242424242425</v>
       </c>
       <c r="G8" t="n">
-        <v>1408492.424242424</v>
+        <v>2580970.707070707</v>
       </c>
       <c r="H8" t="n">
-        <v>69.66515151515152</v>
+        <v>69.31171717171716</v>
       </c>
       <c r="I8" t="n">
-        <v>27.39848484848485</v>
+        <v>28.08</v>
       </c>
       <c r="J8" t="n">
-        <v>183.430303030303</v>
+        <v>181.4822222222222</v>
       </c>
       <c r="K8" t="n">
-        <v>1.13939393939394</v>
+        <v>1.204444444444444</v>
       </c>
       <c r="L8" t="n">
-        <v>68.03030303030305</v>
+        <v>67.04666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>3074621.212121212</v>
+        <v>2133166.666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>69.62575757575758</v>
+        <v>68.56888888888889</v>
       </c>
       <c r="O8" t="n">
-        <v>25.59707602339181</v>
+        <v>24.24339826839827</v>
       </c>
       <c r="P8" t="n">
-        <v>179.3770467836257</v>
+        <v>181.7162878787879</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>1.194318181818182</v>
       </c>
       <c r="R8" t="n">
-        <v>65.30109649122808</v>
+        <v>63.82202380952381</v>
       </c>
       <c r="S8" t="n">
-        <v>1454587.902046784</v>
+        <v>1859379.87012987</v>
       </c>
       <c r="T8" t="n">
-        <v>70.44630847953216</v>
+        <v>68.54431818181817</v>
       </c>
       <c r="U8" t="n">
-        <v>27.06470192958953</v>
+        <v>28.31732040905954</v>
       </c>
       <c r="V8" t="n">
-        <v>183.2764525337213</v>
+        <v>179.8015672250455</v>
       </c>
       <c r="W8" t="n">
-        <v>1.014492753623188</v>
+        <v>1.190493757450279</v>
       </c>
       <c r="X8" t="n">
-        <v>63.34859890561869</v>
+        <v>66.54496455235585</v>
       </c>
       <c r="Y8" t="n">
-        <v>872897.4709258227</v>
+        <v>1245346.87245122</v>
       </c>
       <c r="Z8" t="n">
-        <v>65.62857062733561</v>
+        <v>67.8298795407491</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>23.77979797979798</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="D9" t="n">
-        <v>179.5129292929293</v>
+        <v>182.8939393939394</v>
       </c>
       <c r="E9" t="n">
-        <v>1.074545454545455</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="F9" t="n">
-        <v>66.22161616161615</v>
+        <v>68.39393939393939</v>
       </c>
       <c r="G9" t="n">
-        <v>1430424.242424242</v>
+        <v>2363636.363636364</v>
       </c>
       <c r="H9" t="n">
-        <v>72.22888888888887</v>
+        <v>71.72727272727273</v>
       </c>
       <c r="I9" t="n">
-        <v>26.36363636363636</v>
+        <v>22.44393939393939</v>
       </c>
       <c r="J9" t="n">
-        <v>180.5636363636364</v>
+        <v>180.5530303030303</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>68.25454545454545</v>
+        <v>65.46060606060605</v>
       </c>
       <c r="M9" t="n">
-        <v>2175000</v>
+        <v>1926363.636363636</v>
       </c>
       <c r="N9" t="n">
-        <v>72.54545454545455</v>
+        <v>73.07727272727271</v>
       </c>
       <c r="O9" t="n">
-        <v>23.54262360446571</v>
+        <v>24.86837337909992</v>
       </c>
       <c r="P9" t="n">
-        <v>178.3436602870813</v>
+        <v>180.5846341396971</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.087041467304625</v>
+        <v>1.014880952380952</v>
       </c>
       <c r="R9" t="n">
-        <v>66.00043859649124</v>
+        <v>63.94766808325161</v>
       </c>
       <c r="S9" t="n">
-        <v>1544188.397129187</v>
+        <v>1088320.960916785</v>
       </c>
       <c r="T9" t="n">
-        <v>72.04358054226475</v>
+        <v>68.80923776833389</v>
       </c>
       <c r="U9" t="n">
-        <v>25.29959477862291</v>
+        <v>22.96034356725146</v>
       </c>
       <c r="V9" t="n">
-        <v>182.9713621416946</v>
+        <v>180.872149122807</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>65.41922144351813</v>
+        <v>63.15127923976608</v>
       </c>
       <c r="Y9" t="n">
-        <v>1921685.820573288</v>
+        <v>1298835.404483431</v>
       </c>
       <c r="Z9" t="n">
-        <v>70.70330820075066</v>
+        <v>71.64294590643276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>27.4080808080808</v>
+        <v>27.22727272727273</v>
       </c>
       <c r="D10" t="n">
-        <v>183.0575757575758</v>
+        <v>181.4787878787879</v>
       </c>
       <c r="E10" t="n">
-        <v>1.100505050505051</v>
+        <v>1.193939393939394</v>
       </c>
       <c r="F10" t="n">
-        <v>67.32020202020202</v>
+        <v>68.52878787878788</v>
       </c>
       <c r="G10" t="n">
-        <v>1364924.242424242</v>
+        <v>2020030.303030303</v>
       </c>
       <c r="H10" t="n">
-        <v>70.27929292929292</v>
+        <v>71.57272727272728</v>
       </c>
       <c r="I10" t="n">
-        <v>23.11111111111111</v>
+        <v>24.98686868686869</v>
       </c>
       <c r="J10" t="n">
-        <v>182.3861111111111</v>
+        <v>179.5739393939394</v>
       </c>
       <c r="K10" t="n">
-        <v>1.022222222222222</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>66.08611111111111</v>
+        <v>66.33656565656565</v>
       </c>
       <c r="M10" t="n">
-        <v>1593819.444444444</v>
+        <v>1722348.484848485</v>
       </c>
       <c r="N10" t="n">
-        <v>73.26388888888889</v>
+        <v>71.9979797979798</v>
       </c>
       <c r="O10" t="n">
-        <v>22.98535401002506</v>
+        <v>25.36996651875168</v>
       </c>
       <c r="P10" t="n">
-        <v>183.0119439223058</v>
+        <v>177.8996584475484</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.013157894736842</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.81488878446115</v>
+        <v>65.26349268804512</v>
       </c>
       <c r="S10" t="n">
-        <v>995697.8383458648</v>
+        <v>1139350.426439621</v>
       </c>
       <c r="T10" t="n">
-        <v>70.15072838345864</v>
+        <v>68.78363699623291</v>
       </c>
       <c r="U10" t="n">
-        <v>22.72417675204053</v>
+        <v>26.40285714285715</v>
       </c>
       <c r="V10" t="n">
-        <v>179.979083309879</v>
+        <v>179.4809523809524</v>
       </c>
       <c r="W10" t="n">
-        <v>1.099299043062201</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>62.95826175063327</v>
+        <v>66.09301587301586</v>
       </c>
       <c r="Y10" t="n">
-        <v>1411628.570925978</v>
+        <v>1449616.26984127</v>
       </c>
       <c r="Z10" t="n">
-        <v>72.03322628764424</v>
+        <v>69.95849206349207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>htYUpyrn</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>24.41818181818182</v>
+        <v>25.38939393939394</v>
       </c>
       <c r="D11" t="n">
-        <v>181.9072727272727</v>
+        <v>182.980303030303</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>1.184848484848485</v>
       </c>
       <c r="F11" t="n">
-        <v>67.47999999999999</v>
+        <v>67.68787878787879</v>
       </c>
       <c r="G11" t="n">
-        <v>2451763.636363636</v>
+        <v>2242121.212121212</v>
       </c>
       <c r="H11" t="n">
-        <v>72.60909090909091</v>
+        <v>71.1939393939394</v>
       </c>
       <c r="I11" t="n">
-        <v>25.71515151515151</v>
+        <v>25.19272727272728</v>
       </c>
       <c r="J11" t="n">
-        <v>181.5777777777778</v>
+        <v>181.4545454545454</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>67.96848484848485</v>
+        <v>65.56727272727274</v>
       </c>
       <c r="M11" t="n">
-        <v>3256979.797979798</v>
+        <v>1339618.181818182</v>
       </c>
       <c r="N11" t="n">
-        <v>71.9670707070707</v>
+        <v>70.34727272727272</v>
       </c>
       <c r="O11" t="n">
-        <v>24.24963768115942</v>
+        <v>23.73611264681311</v>
       </c>
       <c r="P11" t="n">
-        <v>181.0010869565218</v>
+        <v>181.8499198363556</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>62.5018115942029</v>
+        <v>63.21401880927809</v>
       </c>
       <c r="S11" t="n">
-        <v>2158038.043478261</v>
+        <v>1248771.983574131</v>
       </c>
       <c r="T11" t="n">
-        <v>67.71992753623189</v>
+        <v>69.33977437466214</v>
       </c>
       <c r="U11" t="n">
-        <v>24.10215617715618</v>
+        <v>25.3014705882353</v>
       </c>
       <c r="V11" t="n">
-        <v>179.5005869130869</v>
+        <v>177.9332817337462</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>65.57434648684651</v>
+        <v>64.6578173374613</v>
       </c>
       <c r="Y11" t="n">
-        <v>2294799.034299034</v>
+        <v>1444351.586687306</v>
       </c>
       <c r="Z11" t="n">
-        <v>71.5803071928072</v>
+        <v>69.5420665634675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.08863636363637</v>
+        <v>24.31388888888889</v>
       </c>
       <c r="D12" t="n">
-        <v>183.75</v>
+        <v>179.7694444444444</v>
       </c>
       <c r="E12" t="n">
-        <v>1.481818181818182</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>71.58636363636363</v>
+        <v>64.98055555555555</v>
       </c>
       <c r="G12" t="n">
-        <v>4704659.090909091</v>
+        <v>1342069.444444444</v>
       </c>
       <c r="H12" t="n">
-        <v>76.64772727272727</v>
+        <v>69.94722222222222</v>
       </c>
       <c r="I12" t="n">
-        <v>26.81636363636363</v>
+        <v>26.65909090909091</v>
       </c>
       <c r="J12" t="n">
-        <v>183.5054545454545</v>
+        <v>177.7068181818182</v>
       </c>
       <c r="K12" t="n">
-        <v>1.130909090909091</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>71.67999999999999</v>
+        <v>69.35454545454544</v>
       </c>
       <c r="M12" t="n">
-        <v>3297909.090909091</v>
+        <v>2285454.545454545</v>
       </c>
       <c r="N12" t="n">
-        <v>74.01636363636364</v>
+        <v>72.09090909090909</v>
       </c>
       <c r="O12" t="n">
-        <v>22.93650793650794</v>
+        <v>21.38456851119895</v>
       </c>
       <c r="P12" t="n">
-        <v>183.6582341269841</v>
+        <v>180.4408102766798</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.058035714285714</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>67.1889880952381</v>
+        <v>58.51717720685112</v>
       </c>
       <c r="S12" t="n">
-        <v>2308774.801587301</v>
+        <v>632031.4558629775</v>
       </c>
       <c r="T12" t="n">
-        <v>75.2936507936508</v>
+        <v>68.55576416337286</v>
       </c>
       <c r="U12" t="n">
-        <v>24.64467787114846</v>
+        <v>25.47001811594203</v>
       </c>
       <c r="V12" t="n">
-        <v>183.4112324929972</v>
+        <v>181.2951539855072</v>
       </c>
       <c r="W12" t="n">
-        <v>1.107002801120448</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>64.26168067226891</v>
+        <v>66.83405797101449</v>
       </c>
       <c r="Y12" t="n">
-        <v>1267851.820728291</v>
+        <v>1502758.605072463</v>
       </c>
       <c r="Z12" t="n">
-        <v>70.42638655462186</v>
+        <v>69.87762681159421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.22000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="D13" t="n">
-        <v>179.56</v>
+        <v>177.78</v>
       </c>
       <c r="E13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="F13" t="n">
-        <v>69.8</v>
+        <v>70.47999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2493500</v>
+        <v>3888000</v>
       </c>
       <c r="H13" t="n">
-        <v>72.66</v>
+        <v>74.14000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>26.58</v>
+        <v>28.91818181818182</v>
       </c>
       <c r="J13" t="n">
-        <v>181.1822222222223</v>
+        <v>180.9954545454545</v>
       </c>
       <c r="K13" t="n">
-        <v>1.064444444444444</v>
+        <v>1.396969696969697</v>
       </c>
       <c r="L13" t="n">
-        <v>67.1888888888889</v>
+        <v>72.5530303030303</v>
       </c>
       <c r="M13" t="n">
-        <v>1839666.666666667</v>
+        <v>3930113.636363637</v>
       </c>
       <c r="N13" t="n">
-        <v>70.89333333333335</v>
+        <v>74.4469696969697</v>
       </c>
       <c r="O13" t="n">
-        <v>26.40372670807453</v>
+        <v>24.85055346700084</v>
       </c>
       <c r="P13" t="n">
-        <v>180.0136645962733</v>
+        <v>180.1069340016709</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.363975155279503</v>
+        <v>1.126065162907268</v>
       </c>
       <c r="R13" t="n">
-        <v>67.33540372670807</v>
+        <v>64.71487050960735</v>
       </c>
       <c r="S13" t="n">
-        <v>3346997.929606625</v>
+        <v>1841389.149958229</v>
       </c>
       <c r="T13" t="n">
-        <v>71.22981366459626</v>
+        <v>69.78282163742691</v>
       </c>
       <c r="U13" t="n">
-        <v>25.79668655868145</v>
+        <v>24.58525167642815</v>
       </c>
       <c r="V13" t="n">
-        <v>180.4664052287582</v>
+        <v>179.4760079789492</v>
       </c>
       <c r="W13" t="n">
-        <v>1.073796533105996</v>
+        <v>1.055952380952381</v>
       </c>
       <c r="X13" t="n">
-        <v>66.03312020460359</v>
+        <v>66.50835667600374</v>
       </c>
       <c r="Y13" t="n">
-        <v>1435218.456947997</v>
+        <v>1934524.764451235</v>
       </c>
       <c r="Z13" t="n">
-        <v>71.12160272804775</v>
+        <v>73.4931117901706</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>27.54080808080808</v>
+        <v>25.3230303030303</v>
       </c>
       <c r="D14" t="n">
-        <v>181.0583838383838</v>
+        <v>177.4848484848485</v>
       </c>
       <c r="E14" t="n">
-        <v>1.259393939393939</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>67.24242424242425</v>
+        <v>68.48888888888889</v>
       </c>
       <c r="G14" t="n">
-        <v>2580970.707070707</v>
+        <v>2509242.424242424</v>
       </c>
       <c r="H14" t="n">
-        <v>69.31171717171716</v>
+        <v>71.66404040404041</v>
       </c>
       <c r="I14" t="n">
-        <v>28.08</v>
+        <v>26.2</v>
       </c>
       <c r="J14" t="n">
-        <v>181.4822222222222</v>
+        <v>179.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1.204444444444444</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>67.04666666666667</v>
+        <v>68.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2133166.666666667</v>
+        <v>3005800</v>
       </c>
       <c r="N14" t="n">
-        <v>68.56888888888889</v>
+        <v>71.75999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>24.24339826839827</v>
+        <v>25.4924788255223</v>
       </c>
       <c r="P14" t="n">
-        <v>181.7162878787879</v>
+        <v>178.9896668548842</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.194318181818182</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>63.82202380952381</v>
+        <v>65.44840767927725</v>
       </c>
       <c r="S14" t="n">
-        <v>1859379.87012987</v>
+        <v>1272323.969508752</v>
       </c>
       <c r="T14" t="n">
-        <v>68.54431818181817</v>
+        <v>69.54748164878599</v>
       </c>
       <c r="U14" t="n">
-        <v>28.31732040905954</v>
+        <v>26.21278260869565</v>
       </c>
       <c r="V14" t="n">
-        <v>179.8015672250455</v>
+        <v>180.0775217391304</v>
       </c>
       <c r="W14" t="n">
-        <v>1.190493757450279</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>66.54496455235585</v>
+        <v>65.69691963109355</v>
       </c>
       <c r="Y14" t="n">
-        <v>1245346.87245122</v>
+        <v>1363072.022397892</v>
       </c>
       <c r="Z14" t="n">
-        <v>67.8298795407491</v>
+        <v>69.3438722002635</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>26.25757575757576</v>
+        <v>26.58214285714286</v>
       </c>
       <c r="D15" t="n">
-        <v>182.8484848484848</v>
+        <v>179.5261904761905</v>
       </c>
       <c r="E15" t="n">
-        <v>1.090909090909091</v>
+        <v>1.175396825396825</v>
       </c>
       <c r="F15" t="n">
-        <v>68.53030303030303</v>
+        <v>69.13809523809523</v>
       </c>
       <c r="G15" t="n">
-        <v>2365151.515151516</v>
+        <v>2600257.936507937</v>
       </c>
       <c r="H15" t="n">
-        <v>71.68181818181817</v>
+        <v>72.5765873015873</v>
       </c>
       <c r="I15" t="n">
-        <v>22.26</v>
+        <v>27.6969696969697</v>
       </c>
       <c r="J15" t="n">
-        <v>180.3</v>
+        <v>180.8484848484848</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>1.060606060606061</v>
       </c>
       <c r="L15" t="n">
-        <v>65.67999999999999</v>
+        <v>66.3030303030303</v>
       </c>
       <c r="M15" t="n">
-        <v>2039000</v>
+        <v>1223257.575757576</v>
       </c>
       <c r="N15" t="n">
-        <v>73.42</v>
+        <v>68.81818181818181</v>
       </c>
       <c r="O15" t="n">
-        <v>24.87184560132215</v>
+        <v>24.4728788616896</v>
       </c>
       <c r="P15" t="n">
-        <v>180.9194555682685</v>
+        <v>178.0788160191613</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.006944444444444</v>
+        <v>1.161545487760322</v>
       </c>
       <c r="R15" t="n">
-        <v>64.20262840071193</v>
+        <v>66.49995432955791</v>
       </c>
       <c r="S15" t="n">
-        <v>1107212.329964404</v>
+        <v>2675430.555555556</v>
       </c>
       <c r="T15" t="n">
-        <v>69.16638062547675</v>
+        <v>72.96358949376852</v>
       </c>
       <c r="U15" t="n">
-        <v>23.35241228070175</v>
+        <v>26.22655906895038</v>
       </c>
       <c r="V15" t="n">
-        <v>181.4065789473684</v>
+        <v>179.4534804567413</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.065277777777778</v>
       </c>
       <c r="X15" t="n">
-        <v>63.35486842105263</v>
+        <v>64.28348155467721</v>
       </c>
       <c r="Y15" t="n">
-        <v>1277069.152046784</v>
+        <v>1047985.47979798</v>
       </c>
       <c r="Z15" t="n">
-        <v>71.19820175438596</v>
+        <v>67.94945652173914</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>dYUosgsB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>27.23272727272727</v>
+        <v>27.72909090909091</v>
       </c>
       <c r="D16" t="n">
-        <v>181.4945454545455</v>
+        <v>179.86</v>
       </c>
       <c r="E16" t="n">
-        <v>1.192727272727273</v>
+        <v>1.094545454545454</v>
       </c>
       <c r="F16" t="n">
-        <v>68.55454545454546</v>
+        <v>67.26363636363638</v>
       </c>
       <c r="G16" t="n">
-        <v>2028936.363636364</v>
+        <v>1443190.909090909</v>
       </c>
       <c r="H16" t="n">
-        <v>71.60727272727273</v>
+        <v>69.27818181818182</v>
       </c>
       <c r="I16" t="n">
-        <v>24.98686868686869</v>
+        <v>25.08863636363637</v>
       </c>
       <c r="J16" t="n">
-        <v>179.5739393939394</v>
+        <v>183.75</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>1.481818181818182</v>
       </c>
       <c r="L16" t="n">
-        <v>66.33656565656565</v>
+        <v>71.58636363636363</v>
       </c>
       <c r="M16" t="n">
-        <v>1722348.484848485</v>
+        <v>4704659.090909091</v>
       </c>
       <c r="N16" t="n">
-        <v>71.9979797979798</v>
+        <v>76.64772727272727</v>
       </c>
       <c r="O16" t="n">
-        <v>25.52729315583536</v>
+        <v>25.68491228070176</v>
       </c>
       <c r="P16" t="n">
-        <v>178.0795901370581</v>
+        <v>179.2208771929825</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>65.21619122565414</v>
+        <v>65.54026315789474</v>
       </c>
       <c r="S16" t="n">
-        <v>1096387.178394212</v>
+        <v>1578663.377192982</v>
       </c>
       <c r="T16" t="n">
-        <v>68.50703106214614</v>
+        <v>70.2934649122807</v>
       </c>
       <c r="U16" t="n">
-        <v>26.40285714285715</v>
+        <v>22.93650793650794</v>
       </c>
       <c r="V16" t="n">
-        <v>179.4809523809524</v>
+        <v>183.6582341269841</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.058035714285714</v>
       </c>
       <c r="X16" t="n">
-        <v>66.09301587301586</v>
+        <v>67.1889880952381</v>
       </c>
       <c r="Y16" t="n">
-        <v>1449616.26984127</v>
+        <v>2308774.801587301</v>
       </c>
       <c r="Z16" t="n">
-        <v>69.95849206349207</v>
+        <v>75.2936507936508</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>U3Cs29yR</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>25.17558922558922</v>
+        <v>26.50185185185185</v>
       </c>
       <c r="D17" t="n">
-        <v>182.3321548821549</v>
+        <v>181.1148148148148</v>
       </c>
       <c r="E17" t="n">
-        <v>1.191582491582492</v>
+        <v>1.072222222222222</v>
       </c>
       <c r="F17" t="n">
-        <v>66.94208754208753</v>
+        <v>67.43518518518518</v>
       </c>
       <c r="G17" t="n">
-        <v>2060681.818181818</v>
+        <v>2105740.740740741</v>
       </c>
       <c r="H17" t="n">
-        <v>70.88249158249158</v>
+        <v>71.15185185185186</v>
       </c>
       <c r="I17" t="n">
-        <v>25.12727272727273</v>
+        <v>23.77979797979798</v>
       </c>
       <c r="J17" t="n">
-        <v>181.1287878787878</v>
+        <v>179.5129292929293</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>1.074545454545455</v>
       </c>
       <c r="L17" t="n">
-        <v>65.37272727272727</v>
+        <v>66.22161616161615</v>
       </c>
       <c r="M17" t="n">
-        <v>1297598.484848485</v>
+        <v>1430424.242424242</v>
       </c>
       <c r="N17" t="n">
-        <v>70.18939393939394</v>
+        <v>72.22888888888887</v>
       </c>
       <c r="O17" t="n">
-        <v>23.80319211017741</v>
+        <v>26.10438165604406</v>
       </c>
       <c r="P17" t="n">
-        <v>182.152293417367</v>
+        <v>180.2577186430127</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.019607843137255</v>
+        <v>1.073401872826425</v>
       </c>
       <c r="R17" t="n">
-        <v>62.80070611577964</v>
+        <v>66.2418858847887</v>
       </c>
       <c r="S17" t="n">
-        <v>1130583.129084967</v>
+        <v>1429646.33317095</v>
       </c>
       <c r="T17" t="n">
-        <v>69.09622432306256</v>
+        <v>70.77990703527787</v>
       </c>
       <c r="U17" t="n">
-        <v>25.33894478844169</v>
+        <v>23.54262360446571</v>
       </c>
       <c r="V17" t="n">
-        <v>177.8566821465429</v>
+        <v>178.3436602870813</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.087041467304625</v>
       </c>
       <c r="X17" t="n">
-        <v>64.80256707946337</v>
+        <v>66.00043859649124</v>
       </c>
       <c r="Y17" t="n">
-        <v>1459503.515221878</v>
+        <v>1544188.397129187</v>
       </c>
       <c r="Z17" t="n">
-        <v>69.66224845201238</v>
+        <v>72.04358054226475</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>vcKjtDdH</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>24.27111111111111</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="D18" t="n">
-        <v>179.8355555555555</v>
+        <v>182.3861111111111</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>1.022222222222222</v>
       </c>
       <c r="F18" t="n">
-        <v>64.88444444444444</v>
+        <v>66.08611111111111</v>
       </c>
       <c r="G18" t="n">
-        <v>1324855.555555556</v>
+        <v>1593819.444444444</v>
       </c>
       <c r="H18" t="n">
-        <v>69.89777777777778</v>
+        <v>73.26388888888889</v>
       </c>
       <c r="I18" t="n">
-        <v>26.64727272727272</v>
+        <v>26.81636363636363</v>
       </c>
       <c r="J18" t="n">
-        <v>177.6054545454545</v>
+        <v>183.5054545454545</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>1.130909090909091</v>
       </c>
       <c r="L18" t="n">
-        <v>69.10363636363635</v>
+        <v>71.67999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>2108863.636363636</v>
+        <v>3297909.090909091</v>
       </c>
       <c r="N18" t="n">
-        <v>71.87272727272727</v>
+        <v>74.01636363636364</v>
       </c>
       <c r="O18" t="n">
-        <v>21.35765480895916</v>
+        <v>22.72417675204053</v>
       </c>
       <c r="P18" t="n">
-        <v>180.5926482213439</v>
+        <v>179.979083309879</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>1.099299043062201</v>
       </c>
       <c r="R18" t="n">
-        <v>58.3937417654809</v>
+        <v>62.95826175063327</v>
       </c>
       <c r="S18" t="n">
-        <v>610425.1646903821</v>
+        <v>1411628.570925978</v>
       </c>
       <c r="T18" t="n">
-        <v>68.52461133069828</v>
+        <v>72.03322628764424</v>
       </c>
       <c r="U18" t="n">
-        <v>25.45601449275362</v>
+        <v>24.64467787114846</v>
       </c>
       <c r="V18" t="n">
-        <v>181.6361231884058</v>
+        <v>183.4112324929972</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.107002801120448</v>
       </c>
       <c r="X18" t="n">
-        <v>66.73724637681158</v>
+        <v>64.26168067226891</v>
       </c>
       <c r="Y18" t="n">
-        <v>1481006.884057971</v>
+        <v>1267851.820728291</v>
       </c>
       <c r="Z18" t="n">
-        <v>69.84210144927536</v>
+        <v>70.42638655462186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>Me49cTqr</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.43333333333333</v>
+        <v>27.54080808080808</v>
       </c>
       <c r="D19" t="n">
-        <v>177.8</v>
+        <v>181.0583838383838</v>
       </c>
       <c r="E19" t="n">
-        <v>1.066666666666667</v>
+        <v>1.259393939393939</v>
       </c>
       <c r="F19" t="n">
-        <v>70.63333333333334</v>
+        <v>67.24242424242425</v>
       </c>
       <c r="G19" t="n">
-        <v>3900833.333333333</v>
+        <v>2580970.707070707</v>
       </c>
       <c r="H19" t="n">
-        <v>74.05000000000001</v>
+        <v>69.31171717171716</v>
       </c>
       <c r="I19" t="n">
-        <v>28.60303030303031</v>
+        <v>25.68855218855219</v>
       </c>
       <c r="J19" t="n">
-        <v>180.7015151515151</v>
+        <v>181.3518518518518</v>
       </c>
       <c r="K19" t="n">
-        <v>1.387878787878788</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>72.35757575757576</v>
+        <v>67.75151515151516</v>
       </c>
       <c r="M19" t="n">
-        <v>4027651.515151516</v>
+        <v>3043779.461279461</v>
       </c>
       <c r="N19" t="n">
-        <v>74.58939393939393</v>
+        <v>71.8429292929293</v>
       </c>
       <c r="O19" t="n">
-        <v>24.49826824004456</v>
+        <v>24.24339826839827</v>
       </c>
       <c r="P19" t="n">
-        <v>180.1154274575327</v>
+        <v>181.7162878787879</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.105054302422724</v>
+        <v>1.194318181818182</v>
       </c>
       <c r="R19" t="n">
-        <v>64.77993595098859</v>
+        <v>63.82202380952381</v>
       </c>
       <c r="S19" t="n">
-        <v>1900719.028473963</v>
+        <v>1859379.87012987</v>
       </c>
       <c r="T19" t="n">
-        <v>70.15235136452242</v>
+        <v>68.54431818181817</v>
       </c>
       <c r="U19" t="n">
-        <v>25.08525167642815</v>
+        <v>24.40804681429681</v>
       </c>
       <c r="V19" t="n">
-        <v>179.6502504031916</v>
+        <v>179.8859057609058</v>
       </c>
       <c r="W19" t="n">
-        <v>1.055952380952381</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>67.4250233426704</v>
+        <v>65.70778873903875</v>
       </c>
       <c r="Y19" t="n">
-        <v>2096077.794754266</v>
+        <v>2131863.778582529</v>
       </c>
       <c r="Z19" t="n">
-        <v>73.7279602750191</v>
+        <v>71.306505994006</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>ImJfuXBN</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.3810606060606</v>
+        <v>26.22000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>176.6742424242424</v>
+        <v>179.56</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="F20" t="n">
-        <v>68.99747474747474</v>
+        <v>69.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2828598.484848485</v>
+        <v>2493500</v>
       </c>
       <c r="H20" t="n">
-        <v>72.10277777777777</v>
+        <v>72.66</v>
       </c>
       <c r="I20" t="n">
-        <v>26.25</v>
+        <v>26.36363636363636</v>
       </c>
       <c r="J20" t="n">
-        <v>179.5333333333333</v>
+        <v>180.5636363636364</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>68.85000000000001</v>
+        <v>68.25454545454545</v>
       </c>
       <c r="M20" t="n">
-        <v>2990166.666666667</v>
+        <v>2175000</v>
       </c>
       <c r="N20" t="n">
-        <v>71.73333333333333</v>
+        <v>72.54545454545455</v>
       </c>
       <c r="O20" t="n">
-        <v>25.29416996047431</v>
+        <v>26.40372670807453</v>
       </c>
       <c r="P20" t="n">
-        <v>178.5049407114624</v>
+        <v>180.0136645962733</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>1.363975155279503</v>
       </c>
       <c r="R20" t="n">
-        <v>65.23908102766799</v>
+        <v>67.33540372670807</v>
       </c>
       <c r="S20" t="n">
-        <v>1289512.104743083</v>
+        <v>3346997.929606625</v>
       </c>
       <c r="T20" t="n">
-        <v>69.50578063241107</v>
+        <v>71.22981366459626</v>
       </c>
       <c r="U20" t="n">
-        <v>26.38565217391304</v>
+        <v>25.29959477862291</v>
       </c>
       <c r="V20" t="n">
-        <v>180.1132125603865</v>
+        <v>182.9713621416946</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>65.94187747035573</v>
+        <v>65.41922144351813</v>
       </c>
       <c r="Y20" t="n">
-        <v>1450997.51866491</v>
+        <v>1921685.820573288</v>
       </c>
       <c r="Z20" t="n">
-        <v>69.38378238910848</v>
+        <v>70.70330820075066</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>0n3Ddmal</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>27.22727272727273</v>
+      </c>
+      <c r="D21" t="n">
+        <v>181.4787878787879</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.193939393939394</v>
+      </c>
+      <c r="F21" t="n">
+        <v>68.52878787878788</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2020030.303030303</v>
+      </c>
+      <c r="H21" t="n">
+        <v>71.57272727272728</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25.3230303030303</v>
+      </c>
+      <c r="J21" t="n">
+        <v>177.4848484848485</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>68.48888888888889</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2509242.424242424</v>
+      </c>
+      <c r="N21" t="n">
+        <v>71.66404040404041</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25.36996651875168</v>
+      </c>
+      <c r="P21" t="n">
+        <v>177.8996584475484</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>65.26349268804512</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1139350.426439621</v>
+      </c>
+      <c r="T21" t="n">
+        <v>68.78363699623291</v>
+      </c>
+      <c r="U21" t="n">
+        <v>25.4924788255223</v>
+      </c>
+      <c r="V21" t="n">
+        <v>178.9896668548842</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>65.44840767927725</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1272323.969508752</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>69.54748164878599</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM4QZAZp</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.19272727272728</v>
+      </c>
+      <c r="D22" t="n">
+        <v>181.4545454545454</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>65.56727272727274</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1339618.181818182</v>
+      </c>
+      <c r="H22" t="n">
+        <v>70.34727272727272</v>
+      </c>
+      <c r="I22" t="n">
+        <v>24.41818181818182</v>
+      </c>
+      <c r="J22" t="n">
+        <v>181.9072727272727</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>67.47999999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2451763.636363636</v>
+      </c>
+      <c r="N22" t="n">
+        <v>72.60909090909091</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25.3014705882353</v>
+      </c>
+      <c r="P22" t="n">
+        <v>177.9332817337462</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>64.6578173374613</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1444351.586687306</v>
+      </c>
+      <c r="T22" t="n">
+        <v>69.5420665634675</v>
+      </c>
+      <c r="U22" t="n">
+        <v>24.24963768115942</v>
+      </c>
+      <c r="V22" t="n">
+        <v>181.0010869565218</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>62.5018115942029</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2158038.043478261</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>67.71992753623189</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>URr9bfCo</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>27.55090909090909</v>
+      </c>
+      <c r="D23" t="n">
+        <v>183.3709090909091</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.130909090909091</v>
+      </c>
+      <c r="F23" t="n">
+        <v>68.05454545454546</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3035363.636363636</v>
+      </c>
+      <c r="H23" t="n">
+        <v>69.51454545454546</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="J23" t="n">
+        <v>182.8939393939394</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="L23" t="n">
+        <v>68.39393939393939</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2363636.363636364</v>
+      </c>
+      <c r="N23" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="O23" t="n">
+        <v>26.8515553589857</v>
+      </c>
+      <c r="P23" t="n">
+        <v>183.088264779596</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>62.96614477369896</v>
+      </c>
+      <c r="S23" t="n">
+        <v>696129.1390240307</v>
+      </c>
+      <c r="T23" t="n">
+        <v>65.4760238832375</v>
+      </c>
+      <c r="U23" t="n">
+        <v>24.86837337909992</v>
+      </c>
+      <c r="V23" t="n">
+        <v>180.5846341396971</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.014880952380952</v>
+      </c>
+      <c r="X23" t="n">
+        <v>63.94766808325161</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1088320.960916785</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>68.80923776833389</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>QDIbviRT</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27.6969696969697</v>
+      </c>
+      <c r="D24" t="n">
+        <v>180.8484848484848</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.060606060606061</v>
+      </c>
+      <c r="F24" t="n">
+        <v>66.3030303030303</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1223257.575757576</v>
+      </c>
+      <c r="H24" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="I24" t="n">
+        <v>24.31388888888889</v>
+      </c>
+      <c r="J24" t="n">
+        <v>179.7694444444444</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>64.98055555555555</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1342069.444444444</v>
+      </c>
+      <c r="N24" t="n">
+        <v>69.94722222222222</v>
+      </c>
+      <c r="O24" t="n">
+        <v>26.22655906895038</v>
+      </c>
+      <c r="P24" t="n">
+        <v>179.4534804567413</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.065277777777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v>64.28348155467721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1047985.47979798</v>
+      </c>
+      <c r="T24" t="n">
+        <v>67.94945652173914</v>
+      </c>
+      <c r="U24" t="n">
+        <v>21.38456851119895</v>
+      </c>
+      <c r="V24" t="n">
+        <v>180.4408102766798</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>58.51717720685112</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>632031.4558629775</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>68.55576416337286</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rVnDcERi</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24.98686868686869</v>
+      </c>
+      <c r="D25" t="n">
+        <v>179.5739393939394</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>66.33656565656565</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1722348.484848485</v>
+      </c>
+      <c r="H25" t="n">
+        <v>71.9979797979798</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26.53939393939394</v>
+      </c>
+      <c r="J25" t="n">
+        <v>181.8136363636364</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.065151515151515</v>
+      </c>
+      <c r="L25" t="n">
+        <v>66.23030303030303</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1858825.757575758</v>
+      </c>
+      <c r="N25" t="n">
+        <v>69.03939393939395</v>
+      </c>
+      <c r="O25" t="n">
+        <v>26.40285714285715</v>
+      </c>
+      <c r="P25" t="n">
+        <v>179.4809523809524</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>66.09301587301586</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1449616.26984127</v>
+      </c>
+      <c r="T25" t="n">
+        <v>69.95849206349207</v>
+      </c>
+      <c r="U25" t="n">
+        <v>24.51080366357069</v>
+      </c>
+      <c r="V25" t="n">
+        <v>180.0906294535358</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.018353174603175</v>
+      </c>
+      <c r="X25" t="n">
+        <v>64.38622598162071</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2541679.512813897</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>70.42302908005307</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhnHdYtb</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>28.91818181818182</v>
+      </c>
+      <c r="D26" t="n">
+        <v>180.9954545454545</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.396969696969697</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72.5530303030303</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3930113.636363637</v>
+      </c>
+      <c r="H26" t="n">
+        <v>74.4469696969697</v>
+      </c>
+      <c r="I26" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="J26" t="n">
+        <v>181.4822222222222</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.204444444444444</v>
+      </c>
+      <c r="L26" t="n">
+        <v>67.04666666666667</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2133166.666666667</v>
+      </c>
+      <c r="N26" t="n">
+        <v>68.56888888888889</v>
+      </c>
+      <c r="O26" t="n">
+        <v>24.58525167642815</v>
+      </c>
+      <c r="P26" t="n">
+        <v>179.4760079789492</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.055952380952381</v>
+      </c>
+      <c r="R26" t="n">
+        <v>66.50835667600374</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1934524.764451235</v>
+      </c>
+      <c r="T26" t="n">
+        <v>73.4931117901706</v>
+      </c>
+      <c r="U26" t="n">
+        <v>28.31732040905954</v>
+      </c>
+      <c r="V26" t="n">
+        <v>179.8015672250455</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.190493757450279</v>
+      </c>
+      <c r="X26" t="n">
+        <v>66.54496455235585</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1245346.87245122</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>67.8298795407491</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>GroLehd4</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26.65909090909091</v>
+      </c>
+      <c r="D27" t="n">
+        <v>177.7068181818182</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>69.35454545454544</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2285454.545454545</v>
+      </c>
+      <c r="H27" t="n">
+        <v>72.09090909090909</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="J27" t="n">
+        <v>177.78</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70.47999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3888000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>74.14000000000001</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25.47001811594203</v>
+      </c>
+      <c r="P27" t="n">
+        <v>181.2951539855072</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>66.83405797101449</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1502758.605072463</v>
+      </c>
+      <c r="T27" t="n">
+        <v>69.87762681159421</v>
+      </c>
+      <c r="U27" t="n">
+        <v>24.85055346700084</v>
+      </c>
+      <c r="V27" t="n">
+        <v>180.1069340016709</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.126065162907268</v>
+      </c>
+      <c r="X27" t="n">
+        <v>64.71487050960735</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1841389.149958229</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>69.78282163742691</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YJuQfCBA</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>26.58214285714286</v>
+      </c>
+      <c r="D28" t="n">
+        <v>179.5261904761905</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.175396825396825</v>
+      </c>
+      <c r="F28" t="n">
+        <v>69.13809523809523</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2600257.936507937</v>
+      </c>
+      <c r="H28" t="n">
+        <v>72.5765873015873</v>
+      </c>
+      <c r="I28" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3005800</v>
+      </c>
+      <c r="N28" t="n">
+        <v>71.75999999999999</v>
+      </c>
+      <c r="O28" t="n">
+        <v>24.4728788616896</v>
+      </c>
+      <c r="P28" t="n">
+        <v>178.0788160191613</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.161545487760322</v>
+      </c>
+      <c r="R28" t="n">
+        <v>66.49995432955791</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2675430.555555556</v>
+      </c>
+      <c r="T28" t="n">
+        <v>72.96358949376852</v>
+      </c>
+      <c r="U28" t="n">
+        <v>26.21278260869565</v>
+      </c>
+      <c r="V28" t="n">
+        <v>180.0775217391304</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>65.69691963109355</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1363072.022397892</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>69.3438722002635</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,1262 +446,786 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.95681818181818</v>
+        <v>24.47569444444444</v>
       </c>
       <c r="D2" t="n">
-        <v>179.8477272727273</v>
+        <v>181.0034722222222</v>
       </c>
       <c r="E2" t="n">
-        <v>1.095454545454546</v>
+        <v>67.65277777777779</v>
       </c>
       <c r="F2" t="n">
-        <v>67.44318181818181</v>
+        <v>4833.333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>1518420.454545455</v>
+        <v>25.14545454545454</v>
       </c>
       <c r="H2" t="n">
-        <v>69.23409090909091</v>
+        <v>182.8909090909091</v>
       </c>
       <c r="I2" t="n">
-        <v>27.52954545454546</v>
+        <v>71.73181818181818</v>
       </c>
       <c r="J2" t="n">
-        <v>183.1909090909091</v>
+        <v>11000</v>
       </c>
       <c r="K2" t="n">
-        <v>1.140909090909091</v>
+        <v>22.39038265954742</v>
       </c>
       <c r="L2" t="n">
-        <v>67.88636363636364</v>
+        <v>179.6634846173405</v>
       </c>
       <c r="M2" t="n">
-        <v>3033977.272727272</v>
-      </c>
-      <c r="N2" t="n">
-        <v>69.25681818181818</v>
-      </c>
+        <v>61.65174294431732</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>25.56666666666667</v>
+        <v>23.48430735930736</v>
       </c>
       <c r="P2" t="n">
-        <v>179.4208333333333</v>
+        <v>182.8602543290043</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>68.50716991341992</v>
       </c>
       <c r="R2" t="n">
-        <v>65.79375</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1768723.958333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>70.55104166666666</v>
-      </c>
-      <c r="U2" t="n">
-        <v>26.74865472504791</v>
-      </c>
-      <c r="V2" t="n">
-        <v>183.031383606074</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>62.94452307238685</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>706806.1606221437</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>65.64766143299425</v>
+        <v>11380.95238095238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>23.61111111111111</v>
+        <v>27.18181818181818</v>
       </c>
       <c r="D3" t="n">
-        <v>179.6866161616161</v>
+        <v>179.7727272727273</v>
       </c>
       <c r="E3" t="n">
-        <v>1.047727272727273</v>
+        <v>69.52272727272727</v>
       </c>
       <c r="F3" t="n">
-        <v>66.11792929292929</v>
+        <v>8409.090909090908</v>
       </c>
       <c r="G3" t="n">
-        <v>1408484.848484849</v>
+        <v>26.68888888888889</v>
       </c>
       <c r="H3" t="n">
-        <v>72.30883838383838</v>
+        <v>180.2222222222222</v>
       </c>
       <c r="I3" t="n">
-        <v>26.54545454545455</v>
+        <v>68.37777777777778</v>
       </c>
       <c r="J3" t="n">
-        <v>180.4545454545455</v>
+        <v>4722.222222222223</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>25.23826777087647</v>
       </c>
       <c r="L3" t="n">
-        <v>68.47727272727272</v>
+        <v>182.2712790430182</v>
       </c>
       <c r="M3" t="n">
-        <v>2205681.818181818</v>
+        <v>65.98510466988728</v>
       </c>
       <c r="N3" t="n">
-        <v>72.54545454545455</v>
+        <v>4649.413388543823</v>
       </c>
       <c r="O3" t="n">
-        <v>23.48036283891547</v>
+        <v>26.08694099378882</v>
       </c>
       <c r="P3" t="n">
-        <v>177.669158692185</v>
+        <v>179.5517460317461</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.087968500797448</v>
+        <v>67.26191338854383</v>
       </c>
       <c r="R3" t="n">
-        <v>66.12554824561404</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1564454.246411483</v>
-      </c>
-      <c r="T3" t="n">
-        <v>72.23155901116428</v>
-      </c>
-      <c r="U3" t="n">
-        <v>25.05631165509682</v>
-      </c>
-      <c r="V3" t="n">
-        <v>183.6005663134819</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>64.84220862257946</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1704039.093898429</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>70.28822616002923</v>
+        <v>3642.857142857143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>27.4080808080808</v>
+        <v>22.59343434343434</v>
       </c>
       <c r="D4" t="n">
-        <v>183.2575757575758</v>
+        <v>179.4441919191919</v>
       </c>
       <c r="E4" t="n">
-        <v>1.100505050505051</v>
-      </c>
-      <c r="F4" t="n">
-        <v>67.29520202020201</v>
-      </c>
+        <v>65.83510101010101</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>1373049.242424242</v>
+        <v>25.94545454545455</v>
       </c>
       <c r="H4" t="n">
-        <v>70.17929292929293</v>
+        <v>183.0363636363636</v>
       </c>
       <c r="I4" t="n">
-        <v>23.19444444444445</v>
-      </c>
-      <c r="J4" t="n">
-        <v>182.3715277777778</v>
-      </c>
+        <v>67.90909090909091</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>1.027777777777778</v>
+        <v>23.10437077542341</v>
       </c>
       <c r="L4" t="n">
-        <v>66.27430555555556</v>
+        <v>177.5253094858358</v>
       </c>
       <c r="M4" t="n">
-        <v>1610329.861111111</v>
-      </c>
-      <c r="N4" t="n">
-        <v>73.27430555555556</v>
-      </c>
+        <v>65.97128237259817</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>23.75271512113617</v>
+        <v>24.875</v>
       </c>
       <c r="P4" t="n">
-        <v>182.5136800334169</v>
+        <v>179.4781055900621</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.027046783625731</v>
+        <v>64.04549689440994</v>
       </c>
       <c r="R4" t="n">
-        <v>62.5110693400167</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1037329.782790309</v>
-      </c>
-      <c r="T4" t="n">
-        <v>69.94413116123643</v>
-      </c>
-      <c r="U4" t="n">
-        <v>22.81698564593302</v>
-      </c>
-      <c r="V4" t="n">
-        <v>179.0915011961723</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.124123803827751</v>
-      </c>
-      <c r="X4" t="n">
-        <v>62.75665071770335</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1402771.00777512</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>72.23270933014354</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>24.15909090909091</v>
+        <v>25.32080808080809</v>
       </c>
       <c r="D5" t="n">
-        <v>182.2704545454545</v>
+        <v>181.5822222222222</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>67.64545454545456</v>
       </c>
       <c r="F5" t="n">
-        <v>66.96363636363637</v>
+        <v>3777.575757575758</v>
       </c>
       <c r="G5" t="n">
-        <v>2174931.818181818</v>
+        <v>25.9</v>
       </c>
       <c r="H5" t="n">
-        <v>72.44318181818183</v>
+        <v>179.725</v>
       </c>
       <c r="I5" t="n">
-        <v>25.58989898989899</v>
+        <v>69.8</v>
       </c>
       <c r="J5" t="n">
-        <v>181.4222222222222</v>
+        <v>4650</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>25.01079386299974</v>
       </c>
       <c r="L5" t="n">
-        <v>67.55636363636364</v>
+        <v>179.8680131143366</v>
       </c>
       <c r="M5" t="n">
-        <v>2894353.535353535</v>
+        <v>67.22570664629488</v>
       </c>
       <c r="N5" t="n">
-        <v>71.75696969696969</v>
+        <v>3891.273554876496</v>
       </c>
       <c r="O5" t="n">
-        <v>24.27038043478261</v>
+        <v>27.01086956521739</v>
       </c>
       <c r="P5" t="n">
-        <v>180.7721920289855</v>
+        <v>178.8354037267081</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>62.95018115942029</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2430255.887681159</v>
-      </c>
-      <c r="T5" t="n">
-        <v>68.01449275362319</v>
-      </c>
-      <c r="U5" t="n">
-        <v>24.68965617715618</v>
-      </c>
-      <c r="V5" t="n">
-        <v>179.8726107226107</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>66.22077505827505</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2156760.343822843</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>71.44399766899767</v>
-      </c>
+        <v>68.58178053830228</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25.08863636363637</v>
+        <v>22.33535353535353</v>
       </c>
       <c r="D6" t="n">
-        <v>183.75</v>
+        <v>180.135101010101</v>
       </c>
       <c r="E6" t="n">
-        <v>1.481818181818182</v>
+        <v>65.67424242424242</v>
       </c>
       <c r="F6" t="n">
-        <v>71.58636363636363</v>
+        <v>2666.666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>4704659.090909091</v>
+        <v>28.125</v>
       </c>
       <c r="H6" t="n">
-        <v>76.64772727272727</v>
+        <v>181.175</v>
       </c>
       <c r="I6" t="n">
-        <v>26.94545454545455</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>183.3318181818182</v>
+        <v>7150</v>
       </c>
       <c r="K6" t="n">
-        <v>1.163636363636364</v>
+        <v>22.81666666666666</v>
       </c>
       <c r="L6" t="n">
-        <v>71.875</v>
+        <v>180.3875</v>
       </c>
       <c r="M6" t="n">
-        <v>3367386.363636364</v>
-      </c>
-      <c r="N6" t="n">
-        <v>74.34545454545454</v>
-      </c>
+        <v>62.95833333333334</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>22.93650793650794</v>
+        <v>25.4143665158371</v>
       </c>
       <c r="P6" t="n">
-        <v>183.6582341269841</v>
+        <v>178.6046945701357</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.058035714285714</v>
-      </c>
-      <c r="R6" t="n">
-        <v>67.1889880952381</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2308774.801587301</v>
-      </c>
-      <c r="T6" t="n">
-        <v>75.2936507936508</v>
-      </c>
-      <c r="U6" t="n">
-        <v>24.52251400560224</v>
-      </c>
-      <c r="V6" t="n">
-        <v>183.5807072829132</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08375350140056</v>
-      </c>
-      <c r="X6" t="n">
-        <v>64.57710084033613</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1357981.442577031</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>70.58298319327731</v>
-      </c>
+        <v>65.99688914027149</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>26.175</v>
+        <v>28.07222222222222</v>
       </c>
       <c r="D7" t="n">
-        <v>179.525</v>
+        <v>181.775</v>
       </c>
       <c r="E7" t="n">
-        <v>1.05</v>
+        <v>67.6888888888889</v>
       </c>
       <c r="F7" t="n">
-        <v>69.8</v>
+        <v>5291.666666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>2486250</v>
+        <v>27.14</v>
       </c>
       <c r="H7" t="n">
-        <v>72.69999999999999</v>
+        <v>181.26</v>
       </c>
       <c r="I7" t="n">
-        <v>26.78</v>
+        <v>68.24000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>180.8933333333334</v>
+        <v>4000</v>
       </c>
       <c r="K7" t="n">
-        <v>1.086666666666666</v>
+        <v>28.61507936507937</v>
       </c>
       <c r="L7" t="n">
-        <v>67.43333333333332</v>
+        <v>179.828529657477</v>
       </c>
       <c r="M7" t="n">
-        <v>2221333.333333333</v>
+        <v>66.87990810359231</v>
       </c>
       <c r="N7" t="n">
-        <v>70.76000000000001</v>
+        <v>3972.988025619605</v>
       </c>
       <c r="O7" t="n">
-        <v>26.50465838509317</v>
+        <v>25.08768453768454</v>
       </c>
       <c r="P7" t="n">
-        <v>180.082298136646</v>
+        <v>177.444289044289</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.357142857142857</v>
-      </c>
-      <c r="R7" t="n">
-        <v>67.54968944099379</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3391030.020703933</v>
-      </c>
-      <c r="T7" t="n">
-        <v>71.31987577639751</v>
-      </c>
-      <c r="U7" t="n">
-        <v>26.01414687614176</v>
-      </c>
-      <c r="V7" t="n">
-        <v>180.1981512605042</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.076971136280599</v>
-      </c>
-      <c r="X7" t="n">
-        <v>66.49026306174645</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1536408.933138473</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>70.9692217756668</v>
-      </c>
+        <v>65.42167832167831</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.7760101010101</v>
+        <v>27.15909090909091</v>
       </c>
       <c r="D8" t="n">
-        <v>180.6729797979798</v>
+        <v>181.5454545454546</v>
       </c>
       <c r="E8" t="n">
-        <v>1.299242424242424</v>
+        <v>67.44545454545454</v>
       </c>
       <c r="F8" t="n">
-        <v>67.5030303030303</v>
+        <v>3913.636363636364</v>
       </c>
       <c r="G8" t="n">
-        <v>2804963.383838383</v>
+        <v>29.09454545454545</v>
       </c>
       <c r="H8" t="n">
-        <v>69.36464646464646</v>
+        <v>181.2636363636364</v>
       </c>
       <c r="I8" t="n">
-        <v>28.125</v>
+        <v>73.04727272727273</v>
       </c>
       <c r="J8" t="n">
-        <v>181.6777777777777</v>
+        <v>16554.54545454545</v>
       </c>
       <c r="K8" t="n">
-        <v>1.180555555555555</v>
+        <v>23.53013738390093</v>
       </c>
       <c r="L8" t="n">
-        <v>67.03333333333333</v>
+        <v>178.5794794891641</v>
       </c>
       <c r="M8" t="n">
-        <v>2088958.333333333</v>
-      </c>
-      <c r="N8" t="n">
-        <v>68.58611111111111</v>
-      </c>
+        <v>65.96062306501548</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>24.09970238095238</v>
+        <v>25.20634669678148</v>
       </c>
       <c r="P8" t="n">
-        <v>181.7135416666667</v>
+        <v>179.9483079239601</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.140625</v>
-      </c>
-      <c r="R8" t="n">
-        <v>63.77752976190476</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1610133.928571429</v>
-      </c>
-      <c r="T8" t="n">
-        <v>68.578125</v>
-      </c>
-      <c r="U8" t="n">
-        <v>28.51621572871573</v>
-      </c>
-      <c r="V8" t="n">
-        <v>179.7410894660895</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.216378066378067</v>
-      </c>
-      <c r="X8" t="n">
-        <v>66.87685786435786</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1316357.503607504</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>67.97213203463204</v>
-      </c>
+        <v>67.42166760775456</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07272727272727</v>
+        <v>28.09772727272728</v>
       </c>
       <c r="D9" t="n">
-        <v>182.8727272727272</v>
+        <v>183.9181818181818</v>
       </c>
       <c r="E9" t="n">
-        <v>1.090909090909091</v>
+        <v>69.25</v>
       </c>
       <c r="F9" t="n">
-        <v>68.34545454545454</v>
+        <v>4859.090909090909</v>
       </c>
       <c r="G9" t="n">
-        <v>2360000</v>
+        <v>24.525</v>
       </c>
       <c r="H9" t="n">
-        <v>71.74545454545455</v>
+        <v>181.45</v>
       </c>
       <c r="I9" t="n">
-        <v>22.37272727272727</v>
-      </c>
-      <c r="J9" t="n">
-        <v>180.3036363636364</v>
-      </c>
+        <v>69.64999999999999</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>25.96090102707749</v>
       </c>
       <c r="L9" t="n">
-        <v>65.31272727272727</v>
+        <v>184.2954014939309</v>
       </c>
       <c r="M9" t="n">
-        <v>1893236.363636364</v>
-      </c>
-      <c r="N9" t="n">
-        <v>73.09272727272726</v>
-      </c>
+        <v>61.69549486461251</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>24.83152173913044</v>
+        <v>24.48913043478261</v>
       </c>
       <c r="P9" t="n">
-        <v>180.3541925465838</v>
+        <v>181.1471920289855</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.017857142857143</v>
-      </c>
-      <c r="R9" t="n">
-        <v>64.11614906832298</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1141037.784679089</v>
-      </c>
-      <c r="T9" t="n">
-        <v>68.96055900621118</v>
-      </c>
-      <c r="U9" t="n">
-        <v>22.92083333333333</v>
-      </c>
-      <c r="V9" t="n">
-        <v>180.615</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>63.03416666666667</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1290497.222222222</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>71.62416666666667</v>
-      </c>
+        <v>62.05434782608696</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>27.2</v>
+        <v>27.96363636363636</v>
       </c>
       <c r="D10" t="n">
-        <v>181.3745454545455</v>
+        <v>180.2727272727273</v>
       </c>
       <c r="E10" t="n">
-        <v>1.196363636363637</v>
+        <v>66.89090909090909</v>
       </c>
       <c r="F10" t="n">
-        <v>68.54363636363637</v>
+        <v>3836.363636363636</v>
       </c>
       <c r="G10" t="n">
-        <v>2017581.818181818</v>
+        <v>26.175</v>
       </c>
       <c r="H10" t="n">
-        <v>71.56</v>
+        <v>181.9</v>
       </c>
       <c r="I10" t="n">
-        <v>24.98358585858586</v>
+        <v>68.05</v>
       </c>
       <c r="J10" t="n">
-        <v>179.9174242424242</v>
+        <v>4800</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>26.0630303030303</v>
       </c>
       <c r="L10" t="n">
-        <v>65.99570707070707</v>
+        <v>178.8027272727273</v>
       </c>
       <c r="M10" t="n">
-        <v>1596685.606060606</v>
+        <v>64.77909090909091</v>
       </c>
       <c r="N10" t="n">
-        <v>71.72247474747475</v>
+        <v>2818.181818181818</v>
       </c>
       <c r="O10" t="n">
-        <v>25.50278335191378</v>
+        <v>24.63422191619123</v>
       </c>
       <c r="P10" t="n">
-        <v>177.7501783723523</v>
+        <v>179.0017757851248</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>65.82207357859531</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1225691.099962839</v>
-      </c>
-      <c r="T10" t="n">
-        <v>69.24624674842066</v>
-      </c>
-      <c r="U10" t="n">
-        <v>26.50357142857143</v>
-      </c>
-      <c r="V10" t="n">
-        <v>179.7011904761905</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>66.34126984126983</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1450270.337301587</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>69.84811507936509</v>
-      </c>
+        <v>63.49161679281816</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.44909090909091</v>
+        <v>24.33333333333334</v>
       </c>
       <c r="D11" t="n">
-        <v>183.3581818181818</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>1.185454545454546</v>
-      </c>
-      <c r="F11" t="n">
-        <v>68.04363636363637</v>
-      </c>
+        <v>64.44444444444444</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>2316454.545454545</v>
+        <v>27.50555555555556</v>
       </c>
       <c r="H11" t="n">
-        <v>71.39636363636365</v>
+        <v>180.0388888888889</v>
       </c>
       <c r="I11" t="n">
-        <v>25.34090909090909</v>
+        <v>67.44166666666668</v>
       </c>
       <c r="J11" t="n">
-        <v>181.6681818181818</v>
+        <v>4900</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>21.50378787878788</v>
       </c>
       <c r="L11" t="n">
-        <v>66.05909090909091</v>
+        <v>179.3465909090909</v>
       </c>
       <c r="M11" t="n">
-        <v>1416022.727272727</v>
-      </c>
-      <c r="N11" t="n">
-        <v>70.75909090909092</v>
-      </c>
+        <v>59.42424242424243</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>23.85980576441103</v>
+        <v>23.83690476190476</v>
       </c>
       <c r="P11" t="n">
-        <v>181.4081390977444</v>
+        <v>182.9376217532468</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>63.58623433583959</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1294702.850877193</v>
-      </c>
-      <c r="T11" t="n">
-        <v>69.36067042606517</v>
-      </c>
-      <c r="U11" t="n">
-        <v>25.24448529411765</v>
-      </c>
-      <c r="V11" t="n">
-        <v>178.0195433436533</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>64.30756578947368</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1384851.248065015</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>69.04523026315789</v>
-      </c>
+        <v>62.71873647186148</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24.18518518518519</v>
+        <v>24.41666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>179.9259259259259</v>
+        <v>181.0555555555555</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>65.27777777777777</v>
       </c>
       <c r="F12" t="n">
-        <v>64.74074074074075</v>
+        <v>5111.111111111111</v>
       </c>
       <c r="G12" t="n">
-        <v>1354259.259259259</v>
+        <v>26.30909090909091</v>
       </c>
       <c r="H12" t="n">
-        <v>69.96296296296295</v>
+        <v>177.9318181818182</v>
       </c>
       <c r="I12" t="n">
-        <v>26.51212121212121</v>
+        <v>69.72954545454544</v>
       </c>
       <c r="J12" t="n">
-        <v>177.7090909090909</v>
+        <v>4268.181818181818</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>26.3078431372549</v>
       </c>
       <c r="L12" t="n">
-        <v>69.47272727272727</v>
+        <v>179.6095811051694</v>
       </c>
       <c r="M12" t="n">
-        <v>2333106.060606061</v>
+        <v>65.90352049910874</v>
       </c>
       <c r="N12" t="n">
-        <v>72.35454545454546</v>
+        <v>4236.244800950683</v>
       </c>
       <c r="O12" t="n">
-        <v>21.80164690382081</v>
+        <v>25.55339912280702</v>
       </c>
       <c r="P12" t="n">
-        <v>180.2544137022398</v>
+        <v>181.415076754386</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>67.03114035087719</v>
       </c>
       <c r="R12" t="n">
-        <v>59.24512516469039</v>
-      </c>
-      <c r="S12" t="n">
-        <v>696930.8300395258</v>
-      </c>
-      <c r="T12" t="n">
-        <v>68.4965744400527</v>
-      </c>
-      <c r="U12" t="n">
-        <v>25.48176328502415</v>
-      </c>
-      <c r="V12" t="n">
-        <v>181.9442632850241</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>66.89468599033817</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1532591.183574879</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>69.83683574879228</v>
+        <v>3129.934210526316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.4</v>
+        <v>26.34545454545454</v>
       </c>
       <c r="D13" t="n">
-        <v>177.775</v>
+        <v>178.8227272727273</v>
       </c>
       <c r="E13" t="n">
-        <v>1.075</v>
+        <v>70.77272727272727</v>
       </c>
       <c r="F13" t="n">
-        <v>70.52500000000001</v>
+        <v>7681.818181818182</v>
       </c>
       <c r="G13" t="n">
-        <v>3875625</v>
+        <v>25.38636363636364</v>
       </c>
       <c r="H13" t="n">
-        <v>74.075</v>
+        <v>177.9545454545455</v>
       </c>
       <c r="I13" t="n">
-        <v>28.88363636363637</v>
+        <v>68.06818181818183</v>
       </c>
       <c r="J13" t="n">
-        <v>181.2309090909091</v>
+        <v>4227.272727272728</v>
       </c>
       <c r="K13" t="n">
-        <v>1.403636363636364</v>
+        <v>25.17845750740488</v>
       </c>
       <c r="L13" t="n">
-        <v>72.66363636363636</v>
+        <v>179.5991968557758</v>
       </c>
       <c r="M13" t="n">
-        <v>3939772.727272728</v>
-      </c>
-      <c r="N13" t="n">
-        <v>74.46363636363637</v>
-      </c>
+        <v>66.44036226930965</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>25.02371814954052</v>
+        <v>25.39449006875478</v>
       </c>
       <c r="P13" t="n">
-        <v>179.9099832915622</v>
+        <v>179.9436401833461</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.144423558897243</v>
-      </c>
-      <c r="R13" t="n">
-        <v>65.06464076858813</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1994499.595342523</v>
-      </c>
-      <c r="T13" t="n">
-        <v>69.89957967836257</v>
-      </c>
-      <c r="U13" t="n">
-        <v>24.82230201171378</v>
-      </c>
-      <c r="V13" t="n">
-        <v>179.571209574739</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.057142857142857</v>
-      </c>
-      <c r="X13" t="n">
-        <v>66.61002801120449</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1853929.717341482</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>73.55173414820474</v>
-      </c>
+        <v>65.85572001527885</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25.18156565656566</v>
+        <v>25.39242424242424</v>
       </c>
       <c r="D14" t="n">
-        <v>177.6338383838384</v>
+        <v>179.1974747474748</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>67.74545454545455</v>
       </c>
       <c r="F14" t="n">
-        <v>68.25</v>
+        <v>5200</v>
       </c>
       <c r="G14" t="n">
-        <v>2416414.141414142</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="H14" t="n">
-        <v>71.63560606060607</v>
+        <v>184.4545454545455</v>
       </c>
       <c r="I14" t="n">
-        <v>26.125</v>
+        <v>69.13636363636364</v>
       </c>
       <c r="J14" t="n">
-        <v>179.45</v>
+        <v>7090.909090909091</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>26.35869565217391</v>
       </c>
       <c r="L14" t="n">
-        <v>68.72500000000001</v>
+        <v>180.1304347826087</v>
       </c>
       <c r="M14" t="n">
-        <v>3029250</v>
-      </c>
-      <c r="N14" t="n">
-        <v>71.8</v>
-      </c>
+        <v>66.16304347826087</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>25.4337803500847</v>
+        <v>24.22842492260062</v>
       </c>
       <c r="P14" t="n">
-        <v>179.089356295878</v>
+        <v>181.7563660990712</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>65.51505505364202</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1358870.870976849</v>
-      </c>
-      <c r="T14" t="n">
-        <v>69.74117024280068</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25.95347826086957</v>
-      </c>
-      <c r="V14" t="n">
-        <v>179.815652173913</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>65.4753162055336</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1361912.944664031</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>69.44025691699605</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>26.58657407407408</v>
-      </c>
-      <c r="D15" t="n">
-        <v>179.5768518518519</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.186111111111111</v>
-      </c>
-      <c r="F15" t="n">
-        <v>69.17962962962963</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2542986.111111111</v>
-      </c>
-      <c r="H15" t="n">
-        <v>72.56157407407407</v>
-      </c>
-      <c r="I15" t="n">
-        <v>27.69090909090909</v>
-      </c>
-      <c r="J15" t="n">
-        <v>180.7818181818182</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.054545454545455</v>
-      </c>
-      <c r="L15" t="n">
-        <v>66.52727272727273</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1253090.909090909</v>
-      </c>
-      <c r="N15" t="n">
-        <v>69.05454545454545</v>
-      </c>
-      <c r="O15" t="n">
-        <v>24.60966301979728</v>
-      </c>
-      <c r="P15" t="n">
-        <v>177.9542708629345</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.166730605285592</v>
-      </c>
-      <c r="R15" t="n">
-        <v>66.78617860187553</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2797458.836553945</v>
-      </c>
-      <c r="T15" t="n">
-        <v>73.18940513403429</v>
-      </c>
-      <c r="U15" t="n">
-        <v>26.21969696969698</v>
-      </c>
-      <c r="V15" t="n">
-        <v>179.3093939393939</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.078333333333334</v>
-      </c>
-      <c r="X15" t="n">
-        <v>64.11409090909092</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1010582.575757576</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>67.83500000000001</v>
-      </c>
+        <v>64.80268962848298</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,776 +456,1018 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.47569444444444</v>
-      </c>
-      <c r="D2" t="n">
-        <v>181.0034722222222</v>
-      </c>
-      <c r="E2" t="n">
-        <v>67.65277777777779</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4833.333333333333</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25.14545454545454</v>
-      </c>
-      <c r="H2" t="n">
-        <v>182.8909090909091</v>
-      </c>
-      <c r="I2" t="n">
-        <v>71.73181818181818</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>22.39038265954742</v>
-      </c>
-      <c r="L2" t="n">
-        <v>179.6634846173405</v>
-      </c>
-      <c r="M2" t="n">
-        <v>61.65174294431732</v>
-      </c>
+          <t>YuZ4CywD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>23.48430735930736</v>
-      </c>
-      <c r="P2" t="n">
-        <v>182.8602543290043</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>68.50716991341992</v>
-      </c>
-      <c r="R2" t="n">
-        <v>11380.95238095238</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>27.18181818181818</v>
-      </c>
-      <c r="D3" t="n">
-        <v>179.7727272727273</v>
-      </c>
-      <c r="E3" t="n">
-        <v>69.52272727272727</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8409.090909090908</v>
-      </c>
-      <c r="G3" t="n">
-        <v>26.68888888888889</v>
-      </c>
-      <c r="H3" t="n">
-        <v>180.2222222222222</v>
-      </c>
-      <c r="I3" t="n">
-        <v>68.37777777777778</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4722.222222222223</v>
-      </c>
-      <c r="K3" t="n">
-        <v>25.23826777087647</v>
-      </c>
-      <c r="L3" t="n">
-        <v>182.2712790430182</v>
-      </c>
-      <c r="M3" t="n">
-        <v>65.98510466988728</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4649.413388543823</v>
-      </c>
-      <c r="O3" t="n">
-        <v>26.08694099378882</v>
-      </c>
-      <c r="P3" t="n">
-        <v>179.5517460317461</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>67.26191338854383</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3642.857142857143</v>
-      </c>
+          <t>UuWb8pb0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>22.59343434343434</v>
-      </c>
-      <c r="D4" t="n">
-        <v>179.4441919191919</v>
-      </c>
-      <c r="E4" t="n">
-        <v>65.83510101010101</v>
-      </c>
+          <t>llHizuVJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>25.94545454545455</v>
-      </c>
-      <c r="H4" t="n">
-        <v>183.0363636363636</v>
-      </c>
-      <c r="I4" t="n">
-        <v>67.90909090909091</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>23.10437077542341</v>
-      </c>
-      <c r="L4" t="n">
-        <v>177.5253094858358</v>
-      </c>
-      <c r="M4" t="n">
-        <v>65.97128237259817</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="P4" t="n">
-        <v>179.4781055900621</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>64.04549689440994</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2750</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>25.32080808080809</v>
-      </c>
-      <c r="D5" t="n">
-        <v>181.5822222222222</v>
-      </c>
-      <c r="E5" t="n">
-        <v>67.64545454545456</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3777.575757575758</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H5" t="n">
-        <v>179.725</v>
-      </c>
-      <c r="I5" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4650</v>
-      </c>
-      <c r="K5" t="n">
-        <v>25.01079386299974</v>
-      </c>
-      <c r="L5" t="n">
-        <v>179.8680131143366</v>
-      </c>
-      <c r="M5" t="n">
-        <v>67.22570664629488</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3891.273554876496</v>
-      </c>
-      <c r="O5" t="n">
-        <v>27.01086956521739</v>
-      </c>
-      <c r="P5" t="n">
-        <v>178.8354037267081</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>68.58178053830228</v>
-      </c>
+        <v>8500</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>22.33535353535353</v>
+        <v>28.08564814814815</v>
       </c>
       <c r="D6" t="n">
-        <v>180.135101010101</v>
+        <v>180.8032407407408</v>
       </c>
       <c r="E6" t="n">
-        <v>65.67424242424242</v>
+        <v>68.35648148148148</v>
       </c>
       <c r="F6" t="n">
-        <v>2666.666666666667</v>
+        <v>6569.444444444445</v>
       </c>
       <c r="G6" t="n">
-        <v>28.125</v>
+        <v>2644039.351851852</v>
       </c>
       <c r="H6" t="n">
-        <v>181.175</v>
+        <v>70.75462962962963</v>
       </c>
       <c r="I6" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7150</v>
-      </c>
-      <c r="K6" t="n">
-        <v>22.81666666666666</v>
-      </c>
-      <c r="L6" t="n">
-        <v>180.3875</v>
-      </c>
-      <c r="M6" t="n">
-        <v>62.95833333333334</v>
-      </c>
+        <v>1.118055555555555</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>25.4143665158371</v>
-      </c>
-      <c r="P6" t="n">
-        <v>178.6046945701357</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>65.99688914027149</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>28.07222222222222</v>
-      </c>
-      <c r="D7" t="n">
-        <v>181.775</v>
-      </c>
-      <c r="E7" t="n">
-        <v>67.6888888888889</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5291.666666666666</v>
-      </c>
-      <c r="G7" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="H7" t="n">
-        <v>181.26</v>
-      </c>
-      <c r="I7" t="n">
-        <v>68.24000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.61507936507937</v>
-      </c>
-      <c r="L7" t="n">
-        <v>179.828529657477</v>
-      </c>
-      <c r="M7" t="n">
-        <v>66.87990810359231</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3972.988025619605</v>
-      </c>
-      <c r="O7" t="n">
-        <v>25.08768453768454</v>
-      </c>
-      <c r="P7" t="n">
-        <v>177.444289044289</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>65.42167832167831</v>
-      </c>
+          <t>MFWf9Qrf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>27.15909090909091</v>
+        <v>28.32563131313131</v>
       </c>
       <c r="D8" t="n">
-        <v>181.5454545454546</v>
+        <v>180.0598484848485</v>
       </c>
       <c r="E8" t="n">
-        <v>67.44545454545454</v>
+        <v>65.90707070707072</v>
       </c>
       <c r="F8" t="n">
-        <v>3913.636363636364</v>
+        <v>5845.075757575758</v>
       </c>
       <c r="G8" t="n">
-        <v>29.09454545454545</v>
+        <v>975779.0404040406</v>
       </c>
       <c r="H8" t="n">
-        <v>181.2636363636364</v>
+        <v>68.84949494949495</v>
       </c>
       <c r="I8" t="n">
-        <v>73.04727272727273</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>16554.54545454545</v>
+        <v>29.09057239057239</v>
       </c>
       <c r="K8" t="n">
-        <v>23.53013738390093</v>
+        <v>180.8716049382716</v>
       </c>
       <c r="L8" t="n">
-        <v>178.5794794891641</v>
+        <v>71.84556677890012</v>
       </c>
       <c r="M8" t="n">
-        <v>65.96062306501548</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>10243.09764309764</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3239682.940516274</v>
+      </c>
       <c r="O8" t="n">
-        <v>25.20634669678148</v>
+        <v>73.93423120089788</v>
       </c>
       <c r="P8" t="n">
-        <v>179.9483079239601</v>
+        <v>1.339169472502806</v>
       </c>
       <c r="Q8" t="n">
-        <v>67.42166760775456</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <v>27.31121687909613</v>
+      </c>
+      <c r="R8" t="n">
+        <v>178.7230908990391</v>
+      </c>
+      <c r="S8" t="n">
+        <v>65.45491243147977</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6108.814817793145</v>
+      </c>
+      <c r="U8" t="n">
+        <v>991670.6882513771</v>
+      </c>
+      <c r="V8" t="n">
+        <v>68.74609945652902</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>26.92855680992936</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>180.5719746484452</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>68.36565326467287</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8577.777777777777</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2542613.966462005</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>72.55549943883277</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.046771637948108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>28.09772727272728</v>
+        <v>26.63194444444445</v>
       </c>
       <c r="D9" t="n">
-        <v>183.9181818181818</v>
+        <v>184.9050925925926</v>
       </c>
       <c r="E9" t="n">
-        <v>69.25</v>
+        <v>68.44675925925925</v>
       </c>
       <c r="F9" t="n">
-        <v>4859.090909090909</v>
+        <v>6293.981481481482</v>
       </c>
       <c r="G9" t="n">
-        <v>24.525</v>
+        <v>2330208.333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>181.45</v>
+        <v>71.4675925925926</v>
       </c>
       <c r="I9" t="n">
-        <v>69.64999999999999</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>1.24537037037037</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.89772727272727</v>
+      </c>
       <c r="K9" t="n">
-        <v>25.96090102707749</v>
+        <v>180.5670454545455</v>
       </c>
       <c r="L9" t="n">
-        <v>184.2954014939309</v>
+        <v>68.65340909090909</v>
       </c>
       <c r="M9" t="n">
-        <v>61.69549486461251</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>6235.227272727273</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1686909.090909091</v>
+      </c>
       <c r="O9" t="n">
-        <v>24.48913043478261</v>
+        <v>71.69090909090909</v>
       </c>
       <c r="P9" t="n">
-        <v>181.1471920289855</v>
+        <v>1.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.05434782608696</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>24.91664823824267</v>
+      </c>
+      <c r="R9" t="n">
+        <v>181.594153889626</v>
+      </c>
+      <c r="S9" t="n">
+        <v>63.20301366160499</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5624.130792667944</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1172540.342891542</v>
+      </c>
+      <c r="V9" t="n">
+        <v>67.66161113568235</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>26.21952850893068</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>177.880614735506</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>64.96706572413095</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5819.77831950658</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1108973.292709706</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>68.95130627223018</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.011363636363636</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>27.96363636363636</v>
+        <v>25.26666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>180.2727272727273</v>
+        <v>179.15</v>
       </c>
       <c r="E10" t="n">
-        <v>66.89090909090909</v>
+        <v>65.41666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>3836.363636363636</v>
+        <v>5916.666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>26.175</v>
+        <v>1557166.666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>181.9</v>
+        <v>70.33333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>68.05</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>4800</v>
+        <v>27.275</v>
       </c>
       <c r="K10" t="n">
-        <v>26.0630303030303</v>
+        <v>180.975</v>
       </c>
       <c r="L10" t="n">
-        <v>178.8027272727273</v>
+        <v>68.82499999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>64.77909090909091</v>
+        <v>6350</v>
       </c>
       <c r="N10" t="n">
-        <v>2818.181818181818</v>
+        <v>2164250</v>
       </c>
       <c r="O10" t="n">
-        <v>24.63422191619123</v>
+        <v>72.3</v>
       </c>
       <c r="P10" t="n">
-        <v>179.0017757851248</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>63.49161679281816</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>23.3766339869281</v>
+      </c>
+      <c r="R10" t="n">
+        <v>178.3218421426542</v>
+      </c>
+      <c r="S10" t="n">
+        <v>61.03561025859619</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5102.408354646207</v>
+      </c>
+      <c r="U10" t="n">
+        <v>830755.8077578858</v>
+      </c>
+      <c r="V10" t="n">
+        <v>68.91192455242965</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24.37136243386243</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>178.819957010582</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>64.09632936507936</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5391.468253968254</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1885368.055555556</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>71.33645833333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>24.33333333333334</v>
+        <v>26.7462962962963</v>
       </c>
       <c r="D11" t="n">
-        <v>179.6666666666667</v>
+        <v>178.7462962962963</v>
       </c>
       <c r="E11" t="n">
-        <v>64.44444444444444</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>70.94259259259259</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6542.592592592592</v>
+      </c>
       <c r="G11" t="n">
-        <v>27.50555555555556</v>
+        <v>4763472.222222222</v>
       </c>
       <c r="H11" t="n">
-        <v>180.0388888888889</v>
+        <v>74.52222222222223</v>
       </c>
       <c r="I11" t="n">
-        <v>67.44166666666668</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>4900</v>
+        <v>29.00198412698413</v>
       </c>
       <c r="K11" t="n">
-        <v>21.50378787878788</v>
+        <v>181.3273809523809</v>
       </c>
       <c r="L11" t="n">
-        <v>179.3465909090909</v>
+        <v>67.12896825396827</v>
       </c>
       <c r="M11" t="n">
-        <v>59.42424242424243</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>6333.333333333334</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1727281.746031746</v>
+      </c>
       <c r="O11" t="n">
-        <v>23.83690476190476</v>
+        <v>68.18253968253968</v>
       </c>
       <c r="P11" t="n">
-        <v>182.9376217532468</v>
+        <v>1.101190476190476</v>
       </c>
       <c r="Q11" t="n">
-        <v>62.71873647186148</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>25.33645617667357</v>
+      </c>
+      <c r="R11" t="n">
+        <v>178.9696240815167</v>
+      </c>
+      <c r="S11" t="n">
+        <v>65.42549730036943</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5758.756546096699</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1722079.552835627</v>
+      </c>
+      <c r="V11" t="n">
+        <v>70.14932001786222</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>29.72387463757433</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>179.134357339427</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>66.75654946189002</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6153.637156617034</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1031468.275468082</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>67.73503796255343</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.007936507936508</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24.41666666666667</v>
+        <v>27.14126984126984</v>
       </c>
       <c r="D12" t="n">
-        <v>181.0555555555555</v>
+        <v>179.2920634920635</v>
       </c>
       <c r="E12" t="n">
-        <v>65.27777777777777</v>
+        <v>69.32857142857144</v>
       </c>
       <c r="F12" t="n">
-        <v>5111.111111111111</v>
+        <v>6761.904761904761</v>
       </c>
       <c r="G12" t="n">
-        <v>26.30909090909091</v>
+        <v>2591587.301587302</v>
       </c>
       <c r="H12" t="n">
-        <v>177.9318181818182</v>
+        <v>72.51269841269843</v>
       </c>
       <c r="I12" t="n">
-        <v>69.72954545454544</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>4268.181818181818</v>
+        <v>25.68253968253968</v>
       </c>
       <c r="K12" t="n">
-        <v>26.3078431372549</v>
+        <v>181.6492063492064</v>
       </c>
       <c r="L12" t="n">
-        <v>179.6095811051694</v>
+        <v>67.24761904761905</v>
       </c>
       <c r="M12" t="n">
-        <v>65.90352049910874</v>
+        <v>5879.36507936508</v>
       </c>
       <c r="N12" t="n">
-        <v>4236.244800950683</v>
+        <v>2136880.952380952</v>
       </c>
       <c r="O12" t="n">
-        <v>25.55339912280702</v>
+        <v>71.63650793650793</v>
       </c>
       <c r="P12" t="n">
-        <v>181.415076754386</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>67.03114035087719</v>
+        <v>27.80152456239412</v>
       </c>
       <c r="R12" t="n">
-        <v>3129.934210526316</v>
+        <v>179.8328627893845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>66.41614906832298</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5988.989271597967</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1189350.649350649</v>
+      </c>
+      <c r="V12" t="n">
+        <v>69.55025409373236</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>26.72269644699985</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>179.0403435058234</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>66.7686937933068</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6089.724310776942</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1829031.217750258</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>70.14953560371518</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>26.34545454545454</v>
+        <v>23.75</v>
       </c>
       <c r="D13" t="n">
-        <v>178.8227272727273</v>
+        <v>181.75</v>
       </c>
       <c r="E13" t="n">
-        <v>70.77272727272727</v>
+        <v>66.625</v>
       </c>
       <c r="F13" t="n">
-        <v>7681.818181818182</v>
+        <v>5625</v>
       </c>
       <c r="G13" t="n">
-        <v>25.38636363636364</v>
+        <v>1490625</v>
       </c>
       <c r="H13" t="n">
-        <v>177.9545454545455</v>
+        <v>70.875</v>
       </c>
       <c r="I13" t="n">
-        <v>68.06818181818183</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4227.272727272728</v>
+        <v>28.91818181818182</v>
       </c>
       <c r="K13" t="n">
-        <v>25.17845750740488</v>
+        <v>183.7038961038961</v>
       </c>
       <c r="L13" t="n">
-        <v>179.5991968557758</v>
+        <v>69.1974025974026</v>
       </c>
       <c r="M13" t="n">
-        <v>66.44036226930965</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>6788.311688311688</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2813136.363636364</v>
+      </c>
       <c r="O13" t="n">
-        <v>25.39449006875478</v>
+        <v>70.62857142857142</v>
       </c>
       <c r="P13" t="n">
-        <v>179.9436401833461</v>
+        <v>1.18961038961039</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.85572001527885</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <v>22.24187564353804</v>
+      </c>
+      <c r="R13" t="n">
+        <v>182.1910044913882</v>
+      </c>
+      <c r="S13" t="n">
+        <v>62.02042529791891</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4746.346549159849</v>
+      </c>
+      <c r="U13" t="n">
+        <v>956434.5897779403</v>
+      </c>
+      <c r="V13" t="n">
+        <v>69.42514014828592</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>27.01334417825101</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>181.9367765946959</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>62.61447303559105</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5492.822636300897</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>735579.081632653</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>66.42031450261264</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.006802721088435</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25.39242424242424</v>
+        <v>27.65974025974026</v>
       </c>
       <c r="D14" t="n">
-        <v>179.1974747474748</v>
+        <v>177.6376623376623</v>
       </c>
       <c r="E14" t="n">
-        <v>67.74545454545455</v>
+        <v>70.34285714285714</v>
       </c>
       <c r="F14" t="n">
-        <v>5200</v>
+        <v>6431.168831168831</v>
       </c>
       <c r="G14" t="n">
-        <v>25.63636363636364</v>
+        <v>3123051.948051948</v>
       </c>
       <c r="H14" t="n">
-        <v>184.4545454545455</v>
+        <v>72.96363636363635</v>
       </c>
       <c r="I14" t="n">
-        <v>69.13636363636364</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>7090.909090909091</v>
+        <v>28.21746031746032</v>
       </c>
       <c r="K14" t="n">
-        <v>26.35869565217391</v>
+        <v>181.063492063492</v>
       </c>
       <c r="L14" t="n">
-        <v>180.1304347826087</v>
+        <v>67.83174603174604</v>
       </c>
       <c r="M14" t="n">
-        <v>66.16304347826087</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>6450.793650793651</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2455603.174603175</v>
+      </c>
       <c r="O14" t="n">
-        <v>24.22842492260062</v>
+        <v>70.03492063492062</v>
       </c>
       <c r="P14" t="n">
-        <v>181.7563660990712</v>
+        <v>1.088888888888889</v>
       </c>
       <c r="Q14" t="n">
-        <v>64.80268962848298</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
+        <v>27.15246675681362</v>
+      </c>
+      <c r="R14" t="n">
+        <v>181.2716012659245</v>
+      </c>
+      <c r="S14" t="n">
+        <v>67.04048447842436</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5986.355662666405</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1644449.249674346</v>
+      </c>
+      <c r="V14" t="n">
+        <v>69.35144621041516</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>25.17858266495004</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>179.6894214207422</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>63.88036228984348</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5512.535086498367</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2439922.128271599</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>70.30963762316522</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.017006802721088</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
